--- a/data/rent_split.xlsx
+++ b/data/rent_split.xlsx
@@ -10,8 +10,12 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Transactions" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Monzo Transactions" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Monzo Reconciliation" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Monzo Categories" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Monzo Transactions'!$A$1:$N$37</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Transactions!$A$1:$F$100</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -23,8 +27,76 @@
 </workbook>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Sep-2025 rows typed from the PDF statement (not in the Monzo export). Oct–Nov rows from the export, checked line by line against the PDFs. Dec-2025–Feb-2026 from the export only (no PDF supplied).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Category = my grouping from payee + reference. Edit any cell in this column; the Categories sheet updates.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Opening balance 01/09/2025 = £0.00 (Sep PDF: closing 4,682.00 − deposits 7,682.00 + outgoings 3,000.00).</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Opening 01/09/2025 derived from Sep PDF: 4,682.00 − 7,682.00 + 3,000.00 = 0.00</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="269">
   <si>
     <t xml:space="preserve">Rent Split – Total per Property</t>
   </si>
@@ -543,19 +615,309 @@
   </si>
   <si>
     <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monzo Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money In (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money Out (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Running Balance (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statement Balance (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faster payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE KULTURE BAR AN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loans received</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF statement Sep-2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCK ERIC NJIAGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other income received</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seyat Can</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building materials (Seyat Can)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monzo export + PDF statement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRABELLE SIEWE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mirabelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUY NOEL DEUFI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">guy exch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monzo-to-Monzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvine Tchega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director transfers (Alvine Tchega)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahmed Sayyed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alino property Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payments to Alino / Ahmed Sayyed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct Debit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Together Commercia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10395974-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortgage – Together Commercial (10395974-002)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10395973-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortgage – Together Commercial (10395973-002)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Alain Kakmeni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sent from Revolut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent received – Kakmeni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monzo export</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAKMENI MR J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALINO LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Building work income (Alino Ltd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alino Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVINE KOUAYA TCHEGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortgage new</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J Kouchoufondjo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jean Calvin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KAKMENI J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvine Kouaya Tchega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monzo Business Account (Alino Property Ltd) – Monthly Reconciliation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue = figures typed from the statement. Black = formulas from the Monzo Transactions sheet. Difference should be 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opening (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculated Closing (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statement Closing (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statement Deposits (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statement Outgoings (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In / Out Check (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statement source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF statement 01/09–30/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF statement 01/10–31/10/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF statement 01/11–30/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monzo export – last balance in month (no PDF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monzo export – last balance to 17/02/2026 (no PDF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rows with a running-balance mismatch:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monzo – Totals by Category and Month (Amount: + in / − out)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMIFS over the Monzo Transactions sheet. Change a Category there and this table follows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account holder moving own money in/out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulture Bar 'loans' (Sep) and Kakmeni J 'Loan' (Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Njiaga (CHASE), Siewe, Deufi (guy exch), Kouchoufondjo – purpose not stated; confirm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumed rent: one payment says 'Rent'; Revolut payments from the same person treated the same. 'Loan' payment is under Loans received.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ahmed Sayyed payment had reference 'Alino property Ltd'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net movement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check vs reconciliation (should be 0)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
     <numFmt numFmtId="166" formatCode="\£#,##0.00;&quot;(£&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="168" formatCode="\£#,##0.00;&quot;-£&quot;#,##0.00;\-"/>
+    <numFmt numFmtId="169" formatCode="0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -636,6 +998,11 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -711,8 +1078,108 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -724,35 +1191,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -760,31 +1215,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -894,6 +1341,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -1080,438 +1531,438 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <f aca="false">COUNTIFS(Transactions!$E:$E,$A5)</f>
         <v>12</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A5,Transactions!$F:$F,"Standing Order")</f>
         <v>8400</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <f aca="false">F5-D5</f>
         <v>16100</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A5)</f>
         <v>24500</v>
       </c>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="G5" s="8"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <f aca="false">COUNTIFS(Transactions!$E:$E,$A6)</f>
         <v>7</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A6,Transactions!$F:$F,"Standing Order")</f>
         <v>15000</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <f aca="false">F6-D6</f>
         <v>2494</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A6)</f>
         <v>17494</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <f aca="false">COUNTIFS(Transactions!$E:$E,$A7)</f>
         <v>12</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A7,Transactions!$F:$F,"Standing Order")</f>
         <v>14400</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <f aca="false">F7-D7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A7)</f>
         <v>14400</v>
       </c>
-      <c r="G7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="G7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <f aca="false">COUNTIFS(Transactions!$E:$E,$A8)</f>
         <v>12</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A8,Transactions!$F:$F,"Standing Order")</f>
         <v>14400</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <f aca="false">F8-D8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A8)</f>
         <v>14400</v>
       </c>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="G8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <f aca="false">COUNTIFS(Transactions!$E:$E,$A9)</f>
         <v>12</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A9,Transactions!$F:$F,"Standing Order")</f>
         <v>13800</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <f aca="false">F9-D9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A9)</f>
         <v>13800</v>
       </c>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="G9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <f aca="false">COUNTIFS(Transactions!$E:$E,$A10)</f>
         <v>6</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A10,Transactions!$F:$F,"Standing Order")</f>
         <v>13200</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <f aca="false">F10-D10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A10)</f>
         <v>13200</v>
       </c>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="G10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <f aca="false">COUNTIFS(Transactions!$E:$E,$A11)</f>
         <v>6</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A11,Transactions!$F:$F,"Standing Order")</f>
         <v>2700</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <f aca="false">F11-D11</f>
         <v>10440</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A11)</f>
         <v>13140</v>
       </c>
-      <c r="G11" s="7"/>
-    </row>
-    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="G11" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <f aca="false">COUNTIFS(Transactions!$E:$E,$A12)</f>
         <v>6</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A12,Transactions!$F:$F,"Standing Order")</f>
         <v>4800</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="7" t="n">
         <f aca="false">F12-D12</f>
         <v>3450</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A12)</f>
         <v>8250</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <f aca="false">COUNTIFS(Transactions!$E:$E,$A13)</f>
         <v>12</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A13,Transactions!$F:$F,"Standing Order")</f>
         <v>7500</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <f aca="false">F13-D13</f>
         <v>0</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A13)</f>
         <v>7500</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="6" t="n">
         <f aca="false">COUNTIFS(Transactions!$E:$E,$A14)</f>
         <v>4</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A14,Transactions!$F:$F,"Standing Order")</f>
         <v>3600</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <f aca="false">F14-D14</f>
         <v>1301.92</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A14)</f>
         <v>4901.92</v>
       </c>
-      <c r="G14" s="7"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="G14" s="8"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="6" t="n">
         <f aca="false">COUNTIFS(Transactions!$E:$E,$A15)</f>
         <v>1</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A15,Transactions!$F:$F,"Standing Order")</f>
         <v>1800</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <f aca="false">F15-D15</f>
         <v>0</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A15)</f>
         <v>1800</v>
       </c>
-      <c r="G15" s="7"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="G15" s="8"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8" t="n">
+      <c r="B16" s="9"/>
+      <c r="C16" s="9" t="n">
         <f aca="false">SUM(C5:C15)</f>
         <v>90</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="10" t="n">
         <f aca="false">SUM(D5:D15)</f>
         <v>99600</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E16" s="10" t="n">
         <f aca="false">SUM(E5:E15)</f>
         <v>33785.92</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="10" t="n">
         <f aca="false">SUM(F5:F15)</f>
         <v>133385.92</v>
       </c>
-      <c r="G16" s="8"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+    <row r="18" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="6" t="n">
         <f aca="false">COUNTIFS(Transactions!$E:$E,$A18)</f>
         <v>4</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A18,Transactions!$F:$F,"Standing Order")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <f aca="false">F18-D18</f>
         <v>7712</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A18)</f>
         <v>7712</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="6" t="n">
         <f aca="false">COUNTIFS(Transactions!$E:$E,$A19)</f>
         <v>5</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A19,Transactions!$F:$F,"Standing Order")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <f aca="false">F19-D19</f>
         <v>1511.47</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <f aca="false">SUMIFS(Transactions!$D:$D,Transactions!$E:$E,$A19)</f>
         <v>1511.47</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11" t="n">
+      <c r="B21" s="12"/>
+      <c r="C21" s="12" t="n">
         <f aca="false">C16+SUM(C18:C19)</f>
         <v>99</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="13" t="n">
         <f aca="false">D16+SUM(D18:D19)</f>
         <v>99600</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="13" t="n">
         <f aca="false">E16+SUM(E18:E19)</f>
         <v>43009.39</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="F21" s="13" t="n">
         <f aca="false">F16+SUM(F18:F19)</f>
         <v>142609.39</v>
       </c>
-      <c r="G21" s="11"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="G21" s="12"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F22" s="14" t="n">
         <f aca="false">F21-Transactions!D101</f>
         <v>0</v>
       </c>
@@ -1535,2019 +1986,2019 @@
   <dimension ref="A1:F101"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="n">
         <v>46001</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>1800</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="n">
+      <c r="F2" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="n">
         <v>45748</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="n">
+      <c r="F3" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="n">
         <v>45778</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="n">
+      <c r="F4" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="n">
         <v>45810</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="n">
+      <c r="F5" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="n">
         <v>45839</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="n">
+      <c r="F6" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="n">
         <v>45870</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="n">
+      <c r="F7" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="n">
         <v>45901</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="n">
+      <c r="F8" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="n">
         <v>45931</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="n">
+      <c r="F9" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="n">
         <v>45964</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="n">
+      <c r="F10" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="n">
         <v>45992</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="n">
+      <c r="F11" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="n">
         <v>46024</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="n">
+      <c r="F12" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="n">
         <v>46055</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14" t="n">
+      <c r="F13" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="n">
         <v>46083</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="n">
+      <c r="F14" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="n">
         <v>45748</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>1150</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="n">
+      <c r="F15" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="n">
         <v>45778</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>1150</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F16" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="n">
+      <c r="F16" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="n">
         <v>45810</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>1150</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="n">
+      <c r="F17" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="n">
         <v>45839</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>1150</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14" t="n">
+      <c r="F18" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="15" t="n">
         <v>45870</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>1150</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14" t="n">
+      <c r="F19" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="n">
         <v>45901</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>1150</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14" t="n">
+      <c r="F20" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="n">
         <v>45931</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>1150</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14" t="n">
+      <c r="F21" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="15" t="n">
         <v>45964</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>1150</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F22" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="n">
+      <c r="F22" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="15" t="n">
         <v>45992</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>1150</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="n">
+      <c r="F23" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="n">
         <v>46024</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>1150</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F24" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="n">
+      <c r="F24" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="n">
         <v>46055</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="D25" s="17" t="n">
         <v>1150</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="n">
+      <c r="F25" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="n">
         <v>46083</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>1150</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14" t="n">
+      <c r="F26" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15" t="n">
         <v>45749</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="n">
+      <c r="F27" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="n">
         <v>45779</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F28" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14" t="n">
+      <c r="F28" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="n">
         <v>45810</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="14" t="n">
+      <c r="F29" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15" t="n">
         <v>45840</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F30" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="n">
+      <c r="F30" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15" t="n">
         <v>45873</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F31" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="n">
+      <c r="F31" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15" t="n">
         <v>45902</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F32" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="n">
+      <c r="F32" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15" t="n">
         <v>45932</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F33" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="n">
+      <c r="F33" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15" t="n">
         <v>45964</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F34" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="n">
+      <c r="F34" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15" t="n">
         <v>45993</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F35" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="14" t="n">
+      <c r="F35" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15" t="n">
         <v>46024</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>700</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F36" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="14" t="n">
+      <c r="F36" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15" t="n">
         <v>46055</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>700</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F37" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="14" t="n">
+      <c r="F37" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="15" t="n">
         <v>46083</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>700</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="F38" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="14" t="n">
+      <c r="F38" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="15" t="n">
         <v>45754</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F39" s="15" t="s">
+      <c r="F39" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="14" t="n">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="15" t="n">
         <v>45783</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="14" t="n">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="15" t="n">
         <v>45813</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="D41" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F41" s="15" t="s">
+      <c r="F41" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="14" t="n">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="15" t="n">
         <v>45842</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F42" s="15" t="s">
+      <c r="F42" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="14" t="n">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="15" t="n">
         <v>45874</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="E43" s="15" t="s">
+      <c r="E43" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F43" s="15" t="s">
+      <c r="F43" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="14" t="n">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="15" t="n">
         <v>45905</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D44" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="E44" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="15" t="s">
+      <c r="F44" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="14" t="n">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="15" t="n">
         <v>45936</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="E45" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F45" s="15" t="s">
+      <c r="F45" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="14" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="15" t="n">
         <v>45968</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="17" t="n">
         <v>2100</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="E46" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F46" s="15" t="s">
+      <c r="F46" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="14" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="15" t="n">
         <v>45996</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>2100</v>
       </c>
-      <c r="E47" s="15" t="s">
+      <c r="E47" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F47" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="14" t="n">
+      <c r="F47" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="15" t="n">
         <v>46027</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="D48" s="17" t="n">
         <v>2100</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F48" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="14" t="n">
+      <c r="F48" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="15" t="n">
         <v>46058</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="D49" s="17" t="n">
         <v>2100</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E49" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F49" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="14" t="n">
+      <c r="F49" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="n">
         <v>46086</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>2100</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F50" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="14" t="n">
+      <c r="F50" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="15" t="n">
         <v>45748</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F51" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="14" t="n">
+      <c r="F51" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="15" t="n">
         <v>45778</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="D52" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E52" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F52" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="14" t="n">
+      <c r="F52" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="15" t="n">
         <v>45810</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="B53" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E53" s="15" t="s">
+      <c r="E53" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F53" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="14" t="n">
+      <c r="F53" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="15" t="n">
         <v>45839</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="D54" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E54" s="15" t="s">
+      <c r="E54" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F54" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="14" t="n">
+      <c r="F54" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="15" t="n">
         <v>45870</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="B55" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E55" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F55" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="14" t="n">
+      <c r="F55" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="n">
         <v>45901</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="B56" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="D56" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E56" s="15" t="s">
+      <c r="E56" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F56" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="14" t="n">
+      <c r="F56" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="n">
         <v>45931</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D57" s="16" t="n">
+      <c r="D57" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E57" s="15" t="s">
+      <c r="E57" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F57" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="14" t="n">
+      <c r="F57" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="15" t="n">
         <v>45964</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="C58" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D58" s="16" t="n">
+      <c r="D58" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E58" s="15" t="s">
+      <c r="E58" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F58" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="14" t="n">
+      <c r="F58" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="15" t="n">
         <v>45992</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C59" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D59" s="16" t="n">
+      <c r="D59" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E59" s="15" t="s">
+      <c r="E59" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F59" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="14" t="n">
+      <c r="F59" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="15" t="n">
         <v>46024</v>
       </c>
-      <c r="B60" s="15" t="s">
+      <c r="B60" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="C60" s="15" t="s">
+      <c r="C60" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D60" s="16" t="n">
+      <c r="D60" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E60" s="15" t="s">
+      <c r="E60" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F60" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="14" t="n">
+      <c r="F60" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="15" t="n">
         <v>46055</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="C61" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D61" s="16" t="n">
+      <c r="D61" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E61" s="15" t="s">
+      <c r="E61" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F61" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="14" t="n">
+      <c r="F61" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="15" t="n">
         <v>46083</v>
       </c>
-      <c r="B62" s="15" t="s">
+      <c r="B62" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C62" s="15" t="s">
+      <c r="C62" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D62" s="16" t="n">
+      <c r="D62" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E62" s="15" t="s">
+      <c r="E62" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F62" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="14" t="n">
+      <c r="F62" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="15" t="n">
         <v>45950</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D63" s="16" t="n">
+      <c r="D63" s="17" t="n">
         <v>2200</v>
       </c>
-      <c r="E63" s="15" t="s">
+      <c r="E63" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F63" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="14" t="n">
+      <c r="F63" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="15" t="n">
         <v>45979</v>
       </c>
-      <c r="B64" s="15" t="s">
+      <c r="B64" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="C64" s="15" t="s">
+      <c r="C64" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D64" s="16" t="n">
+      <c r="D64" s="17" t="n">
         <v>2200</v>
       </c>
-      <c r="E64" s="15" t="s">
+      <c r="E64" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F64" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="14" t="n">
+      <c r="F64" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="15" t="n">
         <v>46009</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="C65" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D65" s="16" t="n">
+      <c r="D65" s="17" t="n">
         <v>2200</v>
       </c>
-      <c r="E65" s="15" t="s">
+      <c r="E65" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F65" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="14" t="n">
+      <c r="F65" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="15" t="n">
         <v>46041</v>
       </c>
-      <c r="B66" s="15" t="s">
+      <c r="B66" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C66" s="15" t="s">
+      <c r="C66" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D66" s="16" t="n">
+      <c r="D66" s="17" t="n">
         <v>2200</v>
       </c>
-      <c r="E66" s="15" t="s">
+      <c r="E66" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F66" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="14" t="n">
+      <c r="F66" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="15" t="n">
         <v>46071</v>
       </c>
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="C67" s="15" t="s">
+      <c r="C67" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D67" s="16" t="n">
+      <c r="D67" s="17" t="n">
         <v>2200</v>
       </c>
-      <c r="E67" s="15" t="s">
+      <c r="E67" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F67" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="14" t="n">
+      <c r="F67" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="15" t="n">
         <v>46099</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="C68" s="15" t="s">
+      <c r="C68" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="16" t="n">
+      <c r="D68" s="17" t="n">
         <v>2200</v>
       </c>
-      <c r="E68" s="15" t="s">
+      <c r="E68" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F68" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="14" t="n">
+      <c r="F68" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="15" t="n">
         <v>45932</v>
       </c>
-      <c r="B69" s="15" t="s">
+      <c r="B69" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="C69" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="D69" s="16" t="n">
+      <c r="D69" s="17" t="n">
         <v>2494</v>
       </c>
-      <c r="E69" s="15" t="s">
+      <c r="E69" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F69" s="15" t="s">
+      <c r="F69" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="14" t="n">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="15" t="n">
         <v>45958</v>
       </c>
-      <c r="B70" s="15" t="s">
+      <c r="B70" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C70" s="15" t="s">
+      <c r="C70" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="16" t="n">
+      <c r="D70" s="17" t="n">
         <v>2500</v>
       </c>
-      <c r="E70" s="15" t="s">
+      <c r="E70" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F70" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="14" t="n">
+      <c r="F70" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="15" t="n">
         <v>45989</v>
       </c>
-      <c r="B71" s="15" t="s">
+      <c r="B71" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="C71" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D71" s="16" t="n">
+      <c r="D71" s="17" t="n">
         <v>2500</v>
       </c>
-      <c r="E71" s="15" t="s">
+      <c r="E71" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F71" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="14" t="n">
+      <c r="F71" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="15" t="n">
         <v>46020</v>
       </c>
-      <c r="B72" s="15" t="s">
+      <c r="B72" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="C72" s="15" t="s">
+      <c r="C72" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D72" s="16" t="n">
+      <c r="D72" s="17" t="n">
         <v>2500</v>
       </c>
-      <c r="E72" s="15" t="s">
+      <c r="E72" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F72" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="14" t="n">
+      <c r="F72" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="15" t="n">
         <v>46050</v>
       </c>
-      <c r="B73" s="15" t="s">
+      <c r="B73" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="C73" s="15" t="s">
+      <c r="C73" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D73" s="16" t="n">
+      <c r="D73" s="17" t="n">
         <v>2500</v>
       </c>
-      <c r="E73" s="15" t="s">
+      <c r="E73" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F73" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="14" t="n">
+      <c r="F73" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="15" t="n">
         <v>46083</v>
       </c>
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="C74" s="15" t="s">
+      <c r="C74" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D74" s="16" t="n">
+      <c r="D74" s="17" t="n">
         <v>2500</v>
       </c>
-      <c r="E74" s="15" t="s">
+      <c r="E74" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F74" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="14" t="n">
+      <c r="F74" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="15" t="n">
         <v>46111</v>
       </c>
-      <c r="B75" s="15" t="s">
+      <c r="B75" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="C75" s="15" t="s">
+      <c r="C75" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="D75" s="16" t="n">
+      <c r="D75" s="17" t="n">
         <v>2500</v>
       </c>
-      <c r="E75" s="15" t="s">
+      <c r="E75" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F75" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="14" t="n">
+      <c r="F75" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="15" t="n">
         <v>45887</v>
       </c>
-      <c r="B76" s="15" t="s">
+      <c r="B76" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="C76" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="D76" s="16" t="n">
+      <c r="D76" s="17" t="n">
         <v>500</v>
       </c>
-      <c r="E76" s="15" t="s">
+      <c r="E76" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F76" s="15" t="s">
+      <c r="F76" s="16" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="14" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="15" t="n">
         <v>45887</v>
       </c>
-      <c r="B77" s="15" t="s">
+      <c r="B77" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="C77" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="D77" s="16" t="n">
+      <c r="D77" s="17" t="n">
         <v>3206</v>
       </c>
-      <c r="E77" s="15" t="s">
+      <c r="E77" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F77" s="15" t="s">
+      <c r="F77" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="14" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="15" t="n">
         <v>45897</v>
       </c>
-      <c r="B78" s="15" t="s">
+      <c r="B78" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="C78" s="15" t="s">
+      <c r="C78" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="D78" s="16" t="n">
+      <c r="D78" s="17" t="n">
         <v>500</v>
       </c>
-      <c r="E78" s="15" t="s">
+      <c r="E78" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F78" s="15" t="s">
+      <c r="F78" s="16" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="14" t="n">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="15" t="n">
         <v>45897</v>
       </c>
-      <c r="B79" s="15" t="s">
+      <c r="B79" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C79" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="D79" s="16" t="n">
+      <c r="D79" s="17" t="n">
         <v>3506</v>
       </c>
-      <c r="E79" s="15" t="s">
+      <c r="E79" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F79" s="15" t="s">
+      <c r="F79" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="14" t="n">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="15" t="n">
         <v>45783</v>
       </c>
-      <c r="B80" s="15" t="s">
+      <c r="B80" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="C80" s="15" t="s">
+      <c r="C80" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="D80" s="16" t="n">
+      <c r="D80" s="17" t="n">
         <v>870</v>
       </c>
-      <c r="E80" s="15" t="s">
+      <c r="E80" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F80" s="15" t="s">
+      <c r="F80" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="14" t="n">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="15" t="n">
         <v>45789</v>
       </c>
-      <c r="B81" s="15" t="s">
+      <c r="B81" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="C81" s="15" t="s">
+      <c r="C81" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="D81" s="16" t="n">
+      <c r="D81" s="17" t="n">
         <v>3480</v>
       </c>
-      <c r="E81" s="15" t="s">
+      <c r="E81" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F81" s="15" t="s">
+      <c r="F81" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="14" t="n">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="15" t="n">
         <v>46020</v>
       </c>
-      <c r="B82" s="15" t="s">
+      <c r="B82" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="C82" s="15" t="s">
+      <c r="C82" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="D82" s="16" t="n">
+      <c r="D82" s="17" t="n">
         <v>6090</v>
       </c>
-      <c r="E82" s="15" t="s">
+      <c r="E82" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F82" s="15" t="s">
+      <c r="F82" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="14" t="n">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="15" t="n">
         <v>46024</v>
       </c>
-      <c r="B83" s="15" t="s">
+      <c r="B83" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="C83" s="15" t="s">
+      <c r="C83" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D83" s="16" t="n">
+      <c r="D83" s="17" t="n">
         <v>900</v>
       </c>
-      <c r="E83" s="15" t="s">
+      <c r="E83" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F83" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="14" t="n">
+      <c r="F83" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="15" t="n">
         <v>46055</v>
       </c>
-      <c r="B84" s="15" t="s">
+      <c r="B84" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="C84" s="15" t="s">
+      <c r="C84" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D84" s="16" t="n">
+      <c r="D84" s="17" t="n">
         <v>900</v>
       </c>
-      <c r="E84" s="15" t="s">
+      <c r="E84" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F84" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="14" t="n">
+      <c r="F84" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="15" t="n">
         <v>46083</v>
       </c>
-      <c r="B85" s="15" t="s">
+      <c r="B85" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="C85" s="15" t="s">
+      <c r="C85" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D85" s="16" t="n">
+      <c r="D85" s="17" t="n">
         <v>900</v>
       </c>
-      <c r="E85" s="15" t="s">
+      <c r="E85" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F85" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="14" t="n">
+      <c r="F85" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="15" t="n">
         <v>46002</v>
       </c>
-      <c r="B86" s="15" t="s">
+      <c r="B86" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="C86" s="15" t="s">
+      <c r="C86" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="D86" s="16" t="n">
+      <c r="D86" s="17" t="n">
         <v>685.52</v>
       </c>
-      <c r="E86" s="15" t="s">
+      <c r="E86" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F86" s="15" t="s">
+      <c r="F86" s="16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="14" t="n">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="15" t="n">
         <v>46050</v>
       </c>
-      <c r="B87" s="15" t="s">
+      <c r="B87" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="C87" s="15" t="s">
+      <c r="C87" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="D87" s="16" t="n">
+      <c r="D87" s="17" t="n">
         <v>232.32</v>
       </c>
-      <c r="E87" s="15" t="s">
+      <c r="E87" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F87" s="15" t="s">
+      <c r="F87" s="16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="14" t="n">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="15" t="n">
         <v>46068</v>
       </c>
-      <c r="B88" s="15" t="s">
+      <c r="B88" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C88" s="15" t="s">
+      <c r="C88" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="D88" s="16" t="n">
+      <c r="D88" s="17" t="n">
         <v>287.52</v>
       </c>
-      <c r="E88" s="15" t="s">
+      <c r="E88" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F88" s="15" t="s">
+      <c r="F88" s="16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="14" t="n">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="15" t="n">
         <v>46068</v>
       </c>
-      <c r="B89" s="15" t="s">
+      <c r="B89" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="C89" s="15" t="s">
+      <c r="C89" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="D89" s="16" t="n">
+      <c r="D89" s="17" t="n">
         <v>18.59</v>
       </c>
-      <c r="E89" s="15" t="s">
+      <c r="E89" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F89" s="15" t="s">
+      <c r="F89" s="16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="14" t="n">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="15" t="n">
         <v>46096</v>
       </c>
-      <c r="B90" s="15" t="s">
+      <c r="B90" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="C90" s="15" t="s">
+      <c r="C90" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="D90" s="16" t="n">
+      <c r="D90" s="17" t="n">
         <v>287.52</v>
       </c>
-      <c r="E90" s="15" t="s">
+      <c r="E90" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="F90" s="15" t="s">
+      <c r="F90" s="16" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="14" t="n">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="15" t="n">
         <v>46034</v>
       </c>
-      <c r="B91" s="15" t="s">
+      <c r="B91" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="C91" s="15" t="s">
+      <c r="C91" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="D91" s="16" t="n">
+      <c r="D91" s="17" t="n">
         <v>101.92</v>
       </c>
-      <c r="E91" s="15" t="s">
+      <c r="E91" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F91" s="15" t="s">
+      <c r="F91" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="14" t="n">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="15" t="n">
         <v>46034</v>
       </c>
-      <c r="B92" s="15" t="s">
+      <c r="B92" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="C92" s="15" t="s">
+      <c r="C92" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="D92" s="16" t="n">
+      <c r="D92" s="17" t="n">
         <v>1200</v>
       </c>
-      <c r="E92" s="15" t="s">
+      <c r="E92" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F92" s="15" t="s">
+      <c r="F92" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="14" t="n">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="15" t="n">
         <v>46055</v>
       </c>
-      <c r="B93" s="15" t="s">
+      <c r="B93" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="C93" s="15" t="s">
+      <c r="C93" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="D93" s="16" t="n">
+      <c r="D93" s="17" t="n">
         <v>1800</v>
       </c>
-      <c r="E93" s="15" t="s">
+      <c r="E93" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F93" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="14" t="n">
+      <c r="F93" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="15" t="n">
         <v>46083</v>
       </c>
-      <c r="B94" s="15" t="s">
+      <c r="B94" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="C94" s="15" t="s">
+      <c r="C94" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="D94" s="16" t="n">
+      <c r="D94" s="17" t="n">
         <v>1800</v>
       </c>
-      <c r="E94" s="15" t="s">
+      <c r="E94" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F94" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="14" t="n">
+      <c r="F94" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="15" t="n">
         <v>45967</v>
       </c>
-      <c r="B95" s="15" t="s">
+      <c r="B95" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="C95" s="15" t="s">
+      <c r="C95" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="D95" s="16" t="n">
+      <c r="D95" s="17" t="n">
         <v>250</v>
       </c>
-      <c r="E95" s="15" t="s">
+      <c r="E95" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F95" s="15" t="s">
+      <c r="F95" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="14" t="n">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="15" t="n">
         <v>45985</v>
       </c>
-      <c r="B96" s="15" t="s">
+      <c r="B96" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="C96" s="15" t="s">
+      <c r="C96" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="D96" s="16" t="n">
+      <c r="D96" s="17" t="n">
         <v>1600</v>
       </c>
-      <c r="E96" s="15" t="s">
+      <c r="E96" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F96" s="15" t="s">
+      <c r="F96" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="14" t="n">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="15" t="n">
         <v>46003</v>
       </c>
-      <c r="B97" s="15" t="s">
+      <c r="B97" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C97" s="15" t="s">
+      <c r="C97" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="D97" s="16" t="n">
+      <c r="D97" s="17" t="n">
         <v>1600</v>
       </c>
-      <c r="E97" s="15" t="s">
+      <c r="E97" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F97" s="15" t="s">
+      <c r="F97" s="16" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="14" t="n">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="15" t="n">
         <v>46029</v>
       </c>
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="C98" s="15" t="s">
+      <c r="C98" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D98" s="16" t="n">
+      <c r="D98" s="17" t="n">
         <v>1600</v>
       </c>
-      <c r="E98" s="15" t="s">
+      <c r="E98" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F98" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="14" t="n">
+      <c r="F98" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="15" t="n">
         <v>46062</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="C99" s="15" t="s">
+      <c r="C99" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D99" s="16" t="n">
+      <c r="D99" s="17" t="n">
         <v>1600</v>
       </c>
-      <c r="E99" s="15" t="s">
+      <c r="E99" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F99" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="14" t="n">
+      <c r="F99" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="15" t="n">
         <v>46090</v>
       </c>
-      <c r="B100" s="15" t="s">
+      <c r="B100" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="C100" s="15" t="s">
+      <c r="C100" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="D100" s="16" t="n">
+      <c r="D100" s="17" t="n">
         <v>1600</v>
       </c>
-      <c r="E100" s="15" t="s">
+      <c r="E100" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F100" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C101" s="17" t="s">
+      <c r="F100" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C101" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="D101" s="18" t="n">
+      <c r="D101" s="19" t="n">
         <f aca="false">SUM(D2:D100)</f>
         <v>142609.39</v>
       </c>
@@ -3563,4 +4014,2722 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:N38"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="20" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B2" s="21" t="str">
+        <f aca="false">TEXT(A2,"yyyy-mm")</f>
+        <v>2025-09</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="H2" s="22" t="n">
+        <f aca="false">IF(J2&gt;0,J2,0)</f>
+        <v>5000</v>
+      </c>
+      <c r="I2" s="22" t="n">
+        <f aca="false">IF(J2&lt;0,-J2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K2" s="22" t="n">
+        <f aca="false">J2</f>
+        <v>5000</v>
+      </c>
+      <c r="L2" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M2" s="22" t="n">
+        <f aca="false">ROUND(K2-L2,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="20" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B3" s="21" t="str">
+        <f aca="false">TEXT(A3,"yyyy-mm")</f>
+        <v>2025-09</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="H3" s="22" t="n">
+        <f aca="false">IF(J3&gt;0,J3,0)</f>
+        <v>1400</v>
+      </c>
+      <c r="I3" s="22" t="n">
+        <f aca="false">IF(J3&lt;0,-J3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="23" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K3" s="22" t="n">
+        <f aca="false">K2+J3</f>
+        <v>6400</v>
+      </c>
+      <c r="L3" s="23" t="n">
+        <v>6400</v>
+      </c>
+      <c r="M3" s="22" t="n">
+        <f aca="false">ROUND(K3-L3,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="n">
+        <v>45921</v>
+      </c>
+      <c r="B4" s="21" t="str">
+        <f aca="false">TEXT(A4,"yyyy-mm")</f>
+        <v>2025-09</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="H4" s="22" t="n">
+        <f aca="false">IF(J4&gt;0,J4,0)</f>
+        <v>1282</v>
+      </c>
+      <c r="I4" s="22" t="n">
+        <f aca="false">IF(J4&lt;0,-J4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="23" t="n">
+        <v>1282</v>
+      </c>
+      <c r="K4" s="22" t="n">
+        <f aca="false">K3+J4</f>
+        <v>7682</v>
+      </c>
+      <c r="L4" s="23" t="n">
+        <v>7682</v>
+      </c>
+      <c r="M4" s="22" t="n">
+        <f aca="false">ROUND(K4-L4,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B5" s="21" t="str">
+        <f aca="false">TEXT(A5,"yyyy-mm")</f>
+        <v>2025-09</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="H5" s="22" t="n">
+        <f aca="false">IF(J5&gt;0,J5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="22" t="n">
+        <f aca="false">IF(J5&lt;0,-J5,0)</f>
+        <v>3000</v>
+      </c>
+      <c r="J5" s="23" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="K5" s="22" t="n">
+        <f aca="false">K4+J5</f>
+        <v>4682</v>
+      </c>
+      <c r="L5" s="23" t="n">
+        <v>4682</v>
+      </c>
+      <c r="M5" s="22" t="n">
+        <f aca="false">ROUND(K5-L5,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B6" s="21" t="str">
+        <f aca="false">TEXT(A6,"yyyy-mm")</f>
+        <v>2025-10</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="H6" s="22" t="n">
+        <f aca="false">IF(J6&gt;0,J6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="22" t="n">
+        <f aca="false">IF(J6&lt;0,-J6,0)</f>
+        <v>1500</v>
+      </c>
+      <c r="J6" s="23" t="n">
+        <v>-1500</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <f aca="false">K5+J6</f>
+        <v>3182</v>
+      </c>
+      <c r="L6" s="23" t="n">
+        <v>3182</v>
+      </c>
+      <c r="M6" s="22" t="n">
+        <f aca="false">ROUND(K6-L6,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B7" s="21" t="str">
+        <f aca="false">TEXT(A7,"yyyy-mm")</f>
+        <v>2025-10</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="H7" s="22" t="n">
+        <f aca="false">IF(J7&gt;0,J7,0)</f>
+        <v>1300</v>
+      </c>
+      <c r="I7" s="22" t="n">
+        <f aca="false">IF(J7&lt;0,-J7,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="23" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <f aca="false">K6+J7</f>
+        <v>4482</v>
+      </c>
+      <c r="L7" s="23" t="n">
+        <v>4482</v>
+      </c>
+      <c r="M7" s="22" t="n">
+        <f aca="false">ROUND(K7-L7,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B8" s="21" t="str">
+        <f aca="false">TEXT(A8,"yyyy-mm")</f>
+        <v>2025-10</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <f aca="false">IF(J8&gt;0,J8,0)</f>
+        <v>1250</v>
+      </c>
+      <c r="I8" s="22" t="n">
+        <f aca="false">IF(J8&lt;0,-J8,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="23" t="n">
+        <v>1250</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <f aca="false">K7+J8</f>
+        <v>5732</v>
+      </c>
+      <c r="L8" s="23" t="n">
+        <v>5732</v>
+      </c>
+      <c r="M8" s="22" t="n">
+        <f aca="false">ROUND(K8-L8,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="n">
+        <v>45936</v>
+      </c>
+      <c r="B9" s="21" t="str">
+        <f aca="false">TEXT(A9,"yyyy-mm")</f>
+        <v>2025-10</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <f aca="false">IF(J9&gt;0,J9,0)</f>
+        <v>500</v>
+      </c>
+      <c r="I9" s="22" t="n">
+        <f aca="false">IF(J9&lt;0,-J9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <f aca="false">K8+J9</f>
+        <v>6232</v>
+      </c>
+      <c r="L9" s="23" t="n">
+        <v>6232</v>
+      </c>
+      <c r="M9" s="22" t="n">
+        <f aca="false">ROUND(K9-L9,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B10" s="21" t="str">
+        <f aca="false">TEXT(A10,"yyyy-mm")</f>
+        <v>2025-10</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="H10" s="22" t="n">
+        <f aca="false">IF(J10&gt;0,J10,0)</f>
+        <v>2500</v>
+      </c>
+      <c r="I10" s="22" t="n">
+        <f aca="false">IF(J10&lt;0,-J10,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K10" s="22" t="n">
+        <f aca="false">K9+J10</f>
+        <v>8732</v>
+      </c>
+      <c r="L10" s="23" t="n">
+        <v>8732</v>
+      </c>
+      <c r="M10" s="22" t="n">
+        <f aca="false">ROUND(K10-L10,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B11" s="21" t="str">
+        <f aca="false">TEXT(A11,"yyyy-mm")</f>
+        <v>2025-10</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="H11" s="22" t="n">
+        <f aca="false">IF(J11&gt;0,J11,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="22" t="n">
+        <f aca="false">IF(J11&lt;0,-J11,0)</f>
+        <v>1000</v>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="K11" s="22" t="n">
+        <f aca="false">K10+J11</f>
+        <v>7732</v>
+      </c>
+      <c r="L11" s="23" t="n">
+        <v>7732</v>
+      </c>
+      <c r="M11" s="22" t="n">
+        <f aca="false">ROUND(K11-L11,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B12" s="21" t="str">
+        <f aca="false">TEXT(A12,"yyyy-mm")</f>
+        <v>2025-10</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="H12" s="22" t="n">
+        <f aca="false">IF(J12&gt;0,J12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="22" t="n">
+        <f aca="false">IF(J12&lt;0,-J12,0)</f>
+        <v>2000</v>
+      </c>
+      <c r="J12" s="23" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="K12" s="22" t="n">
+        <f aca="false">K11+J12</f>
+        <v>5732</v>
+      </c>
+      <c r="L12" s="23" t="n">
+        <v>5732</v>
+      </c>
+      <c r="M12" s="22" t="n">
+        <f aca="false">ROUND(K12-L12,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B13" s="21" t="str">
+        <f aca="false">TEXT(A13,"yyyy-mm")</f>
+        <v>2025-10</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="H13" s="22" t="n">
+        <f aca="false">IF(J13&gt;0,J13,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="22" t="n">
+        <f aca="false">IF(J13&lt;0,-J13,0)</f>
+        <v>2139.83</v>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>-2139.83</v>
+      </c>
+      <c r="K13" s="22" t="n">
+        <f aca="false">K12+J13</f>
+        <v>3592.17</v>
+      </c>
+      <c r="L13" s="23" t="n">
+        <v>3592.17</v>
+      </c>
+      <c r="M13" s="22" t="n">
+        <f aca="false">ROUND(K13-L13,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B14" s="21" t="str">
+        <f aca="false">TEXT(A14,"yyyy-mm")</f>
+        <v>2025-10</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <f aca="false">IF(J14&gt;0,J14,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="22" t="n">
+        <f aca="false">IF(J14&lt;0,-J14,0)</f>
+        <v>1160.58</v>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>-1160.58</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <f aca="false">K13+J14</f>
+        <v>2431.59</v>
+      </c>
+      <c r="L14" s="23" t="n">
+        <v>2431.59</v>
+      </c>
+      <c r="M14" s="22" t="n">
+        <f aca="false">ROUND(K14-L14,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B15" s="21" t="str">
+        <f aca="false">TEXT(A15,"yyyy-mm")</f>
+        <v>2025-11</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="H15" s="22" t="n">
+        <f aca="false">IF(J15&gt;0,J15,0)</f>
+        <v>1000</v>
+      </c>
+      <c r="I15" s="22" t="n">
+        <f aca="false">IF(J15&lt;0,-J15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K15" s="22" t="n">
+        <f aca="false">K14+J15</f>
+        <v>3431.59</v>
+      </c>
+      <c r="L15" s="23" t="n">
+        <v>3431.59</v>
+      </c>
+      <c r="M15" s="22" t="n">
+        <f aca="false">ROUND(K15-L15,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B16" s="21" t="str">
+        <f aca="false">TEXT(A16,"yyyy-mm")</f>
+        <v>2025-11</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <f aca="false">IF(J16&gt;0,J16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="22" t="n">
+        <f aca="false">IF(J16&lt;0,-J16,0)</f>
+        <v>2139.83</v>
+      </c>
+      <c r="J16" s="23" t="n">
+        <v>-2139.83</v>
+      </c>
+      <c r="K16" s="22" t="n">
+        <f aca="false">K15+J16</f>
+        <v>1291.76</v>
+      </c>
+      <c r="L16" s="23" t="n">
+        <v>1291.76</v>
+      </c>
+      <c r="M16" s="22" t="n">
+        <f aca="false">ROUND(K16-L16,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B17" s="21" t="str">
+        <f aca="false">TEXT(A17,"yyyy-mm")</f>
+        <v>2025-11</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="H17" s="22" t="n">
+        <f aca="false">IF(J17&gt;0,J17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="22" t="n">
+        <f aca="false">IF(J17&lt;0,-J17,0)</f>
+        <v>1160.58</v>
+      </c>
+      <c r="J17" s="23" t="n">
+        <v>-1160.58</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <f aca="false">K16+J17</f>
+        <v>131.18</v>
+      </c>
+      <c r="L17" s="23" t="n">
+        <v>131.18</v>
+      </c>
+      <c r="M17" s="22" t="n">
+        <f aca="false">ROUND(K17-L17,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B18" s="21" t="str">
+        <f aca="false">TEXT(A18,"yyyy-mm")</f>
+        <v>2025-12</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="H18" s="22" t="n">
+        <f aca="false">IF(J18&gt;0,J18,0)</f>
+        <v>2000</v>
+      </c>
+      <c r="I18" s="22" t="n">
+        <f aca="false">IF(J18&lt;0,-J18,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K18" s="22" t="n">
+        <f aca="false">K17+J18</f>
+        <v>2131.18</v>
+      </c>
+      <c r="L18" s="23" t="n">
+        <v>2131.18</v>
+      </c>
+      <c r="M18" s="22" t="n">
+        <f aca="false">ROUND(K18-L18,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B19" s="21" t="str">
+        <f aca="false">TEXT(A19,"yyyy-mm")</f>
+        <v>2025-12</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="H19" s="22" t="n">
+        <f aca="false">IF(J19&gt;0,J19,0)</f>
+        <v>1100</v>
+      </c>
+      <c r="I19" s="22" t="n">
+        <f aca="false">IF(J19&lt;0,-J19,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="23" t="n">
+        <v>1100</v>
+      </c>
+      <c r="K19" s="22" t="n">
+        <f aca="false">K18+J19</f>
+        <v>3231.18</v>
+      </c>
+      <c r="L19" s="23" t="n">
+        <v>3231.18</v>
+      </c>
+      <c r="M19" s="22" t="n">
+        <f aca="false">ROUND(K19-L19,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B20" s="21" t="str">
+        <f aca="false">TEXT(A20,"yyyy-mm")</f>
+        <v>2025-12</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="H20" s="22" t="n">
+        <f aca="false">IF(J20&gt;0,J20,0)</f>
+        <v>100</v>
+      </c>
+      <c r="I20" s="22" t="n">
+        <f aca="false">IF(J20&lt;0,-J20,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="K20" s="22" t="n">
+        <f aca="false">K19+J20</f>
+        <v>3331.18</v>
+      </c>
+      <c r="L20" s="23" t="n">
+        <v>3331.18</v>
+      </c>
+      <c r="M20" s="22" t="n">
+        <f aca="false">ROUND(K20-L20,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N20" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B21" s="21" t="str">
+        <f aca="false">TEXT(A21,"yyyy-mm")</f>
+        <v>2025-12</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="H21" s="22" t="n">
+        <f aca="false">IF(J21&gt;0,J21,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="22" t="n">
+        <f aca="false">IF(J21&lt;0,-J21,0)</f>
+        <v>1160.58</v>
+      </c>
+      <c r="J21" s="23" t="n">
+        <v>-1160.58</v>
+      </c>
+      <c r="K21" s="22" t="n">
+        <f aca="false">K20+J21</f>
+        <v>2170.6</v>
+      </c>
+      <c r="L21" s="23" t="n">
+        <v>2170.6</v>
+      </c>
+      <c r="M21" s="22" t="n">
+        <f aca="false">ROUND(K21-L21,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N21" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B22" s="21" t="str">
+        <f aca="false">TEXT(A22,"yyyy-mm")</f>
+        <v>2025-12</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="H22" s="22" t="n">
+        <f aca="false">IF(J22&gt;0,J22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="22" t="n">
+        <f aca="false">IF(J22&lt;0,-J22,0)</f>
+        <v>2139.83</v>
+      </c>
+      <c r="J22" s="23" t="n">
+        <v>-2139.83</v>
+      </c>
+      <c r="K22" s="22" t="n">
+        <f aca="false">K21+J22</f>
+        <v>30.7700000000004</v>
+      </c>
+      <c r="L22" s="23" t="n">
+        <v>30.77</v>
+      </c>
+      <c r="M22" s="22" t="n">
+        <f aca="false">ROUND(K22-L22,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B23" s="21" t="str">
+        <f aca="false">TEXT(A23,"yyyy-mm")</f>
+        <v>2025-12</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="H23" s="22" t="n">
+        <f aca="false">IF(J23&gt;0,J23,0)</f>
+        <v>800</v>
+      </c>
+      <c r="I23" s="22" t="n">
+        <f aca="false">IF(J23&lt;0,-J23,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="23" t="n">
+        <v>800</v>
+      </c>
+      <c r="K23" s="22" t="n">
+        <f aca="false">K22+J23</f>
+        <v>830.77</v>
+      </c>
+      <c r="L23" s="23" t="n">
+        <v>830.77</v>
+      </c>
+      <c r="M23" s="22" t="n">
+        <f aca="false">ROUND(K23-L23,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B24" s="21" t="str">
+        <f aca="false">TEXT(A24,"yyyy-mm")</f>
+        <v>2025-12</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="H24" s="22" t="n">
+        <f aca="false">IF(J24&gt;0,J24,0)</f>
+        <v>500</v>
+      </c>
+      <c r="I24" s="22" t="n">
+        <f aca="false">IF(J24&lt;0,-J24,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="K24" s="22" t="n">
+        <f aca="false">K23+J24</f>
+        <v>1330.77</v>
+      </c>
+      <c r="L24" s="23" t="n">
+        <v>1330.77</v>
+      </c>
+      <c r="M24" s="22" t="n">
+        <f aca="false">ROUND(K24-L24,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B25" s="21" t="str">
+        <f aca="false">TEXT(A25,"yyyy-mm")</f>
+        <v>2025-12</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="H25" s="22" t="n">
+        <f aca="false">IF(J25&gt;0,J25,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="22" t="n">
+        <f aca="false">IF(J25&lt;0,-J25,0)</f>
+        <v>200</v>
+      </c>
+      <c r="J25" s="23" t="n">
+        <v>-200</v>
+      </c>
+      <c r="K25" s="22" t="n">
+        <f aca="false">K24+J25</f>
+        <v>1130.77</v>
+      </c>
+      <c r="L25" s="23" t="n">
+        <v>1130.77</v>
+      </c>
+      <c r="M25" s="22" t="n">
+        <f aca="false">ROUND(K25-L25,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N25" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B26" s="21" t="str">
+        <f aca="false">TEXT(A26,"yyyy-mm")</f>
+        <v>2025-12</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="H26" s="22" t="n">
+        <f aca="false">IF(J26&gt;0,J26,0)</f>
+        <v>800</v>
+      </c>
+      <c r="I26" s="22" t="n">
+        <f aca="false">IF(J26&lt;0,-J26,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="23" t="n">
+        <v>800</v>
+      </c>
+      <c r="K26" s="22" t="n">
+        <f aca="false">K25+J26</f>
+        <v>1930.77</v>
+      </c>
+      <c r="L26" s="23" t="n">
+        <v>1930.77</v>
+      </c>
+      <c r="M26" s="22" t="n">
+        <f aca="false">ROUND(K26-L26,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B27" s="21" t="str">
+        <f aca="false">TEXT(A27,"yyyy-mm")</f>
+        <v>2026-01</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="H27" s="22" t="n">
+        <f aca="false">IF(J27&gt;0,J27,0)</f>
+        <v>900</v>
+      </c>
+      <c r="I27" s="22" t="n">
+        <f aca="false">IF(J27&lt;0,-J27,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="23" t="n">
+        <v>900</v>
+      </c>
+      <c r="K27" s="22" t="n">
+        <f aca="false">K26+J27</f>
+        <v>2830.77</v>
+      </c>
+      <c r="L27" s="23" t="n">
+        <v>2830.77</v>
+      </c>
+      <c r="M27" s="22" t="n">
+        <f aca="false">ROUND(K27-L27,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N27" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B28" s="21" t="str">
+        <f aca="false">TEXT(A28,"yyyy-mm")</f>
+        <v>2026-01</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="H28" s="22" t="n">
+        <f aca="false">IF(J28&gt;0,J28,0)</f>
+        <v>400</v>
+      </c>
+      <c r="I28" s="22" t="n">
+        <f aca="false">IF(J28&lt;0,-J28,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="K28" s="22" t="n">
+        <f aca="false">K27+J28</f>
+        <v>3230.77</v>
+      </c>
+      <c r="L28" s="23" t="n">
+        <v>3230.77</v>
+      </c>
+      <c r="M28" s="22" t="n">
+        <f aca="false">ROUND(K28-L28,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N28" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B29" s="21" t="str">
+        <f aca="false">TEXT(A29,"yyyy-mm")</f>
+        <v>2026-01</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="H29" s="22" t="n">
+        <f aca="false">IF(J29&gt;0,J29,0)</f>
+        <v>200</v>
+      </c>
+      <c r="I29" s="22" t="n">
+        <f aca="false">IF(J29&lt;0,-J29,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="K29" s="22" t="n">
+        <f aca="false">K28+J29</f>
+        <v>3430.77</v>
+      </c>
+      <c r="L29" s="23" t="n">
+        <v>3430.77</v>
+      </c>
+      <c r="M29" s="22" t="n">
+        <f aca="false">ROUND(K29-L29,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N29" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="n">
+        <v>46040</v>
+      </c>
+      <c r="B30" s="21" t="str">
+        <f aca="false">TEXT(A30,"yyyy-mm")</f>
+        <v>2026-01</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="H30" s="22" t="n">
+        <f aca="false">IF(J30&gt;0,J30,0)</f>
+        <v>300</v>
+      </c>
+      <c r="I30" s="22" t="n">
+        <f aca="false">IF(J30&lt;0,-J30,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="K30" s="22" t="n">
+        <f aca="false">K29+J30</f>
+        <v>3730.77</v>
+      </c>
+      <c r="L30" s="23" t="n">
+        <v>3730.77</v>
+      </c>
+      <c r="M30" s="22" t="n">
+        <f aca="false">ROUND(K30-L30,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N30" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B31" s="21" t="str">
+        <f aca="false">TEXT(A31,"yyyy-mm")</f>
+        <v>2026-01</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="H31" s="22" t="n">
+        <f aca="false">IF(J31&gt;0,J31,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <f aca="false">IF(J31&lt;0,-J31,0)</f>
+        <v>1160.58</v>
+      </c>
+      <c r="J31" s="23" t="n">
+        <v>-1160.58</v>
+      </c>
+      <c r="K31" s="22" t="n">
+        <f aca="false">K30+J31</f>
+        <v>2570.19</v>
+      </c>
+      <c r="L31" s="23" t="n">
+        <v>2570.19</v>
+      </c>
+      <c r="M31" s="22" t="n">
+        <f aca="false">ROUND(K31-L31,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N31" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B32" s="21" t="str">
+        <f aca="false">TEXT(A32,"yyyy-mm")</f>
+        <v>2026-01</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G32" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="H32" s="22" t="n">
+        <f aca="false">IF(J32&gt;0,J32,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="22" t="n">
+        <f aca="false">IF(J32&lt;0,-J32,0)</f>
+        <v>2139.83</v>
+      </c>
+      <c r="J32" s="23" t="n">
+        <v>-2139.83</v>
+      </c>
+      <c r="K32" s="22" t="n">
+        <f aca="false">K31+J32</f>
+        <v>430.360000000001</v>
+      </c>
+      <c r="L32" s="23" t="n">
+        <v>430.36</v>
+      </c>
+      <c r="M32" s="22" t="n">
+        <f aca="false">ROUND(K32-L32,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N32" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B33" s="21" t="str">
+        <f aca="false">TEXT(A33,"yyyy-mm")</f>
+        <v>2026-01</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="H33" s="22" t="n">
+        <f aca="false">IF(J33&gt;0,J33,0)</f>
+        <v>600</v>
+      </c>
+      <c r="I33" s="22" t="n">
+        <f aca="false">IF(J33&lt;0,-J33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="23" t="n">
+        <v>600</v>
+      </c>
+      <c r="K33" s="22" t="n">
+        <f aca="false">K32+J33</f>
+        <v>1030.36</v>
+      </c>
+      <c r="L33" s="23" t="n">
+        <v>1030.36</v>
+      </c>
+      <c r="M33" s="22" t="n">
+        <f aca="false">ROUND(K33-L33,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B34" s="21" t="str">
+        <f aca="false">TEXT(A34,"yyyy-mm")</f>
+        <v>2026-02</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="H34" s="22" t="n">
+        <f aca="false">IF(J34&gt;0,J34,0)</f>
+        <v>1000</v>
+      </c>
+      <c r="I34" s="22" t="n">
+        <f aca="false">IF(J34&lt;0,-J34,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K34" s="22" t="n">
+        <f aca="false">K33+J34</f>
+        <v>2030.36</v>
+      </c>
+      <c r="L34" s="23" t="n">
+        <v>2030.36</v>
+      </c>
+      <c r="M34" s="22" t="n">
+        <f aca="false">ROUND(K34-L34,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N34" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B35" s="21" t="str">
+        <f aca="false">TEXT(A35,"yyyy-mm")</f>
+        <v>2026-02</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="H35" s="22" t="n">
+        <f aca="false">IF(J35&gt;0,J35,0)</f>
+        <v>1400</v>
+      </c>
+      <c r="I35" s="22" t="n">
+        <f aca="false">IF(J35&lt;0,-J35,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="23" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K35" s="22" t="n">
+        <f aca="false">K34+J35</f>
+        <v>3430.36</v>
+      </c>
+      <c r="L35" s="23" t="n">
+        <v>3430.36</v>
+      </c>
+      <c r="M35" s="22" t="n">
+        <f aca="false">ROUND(K35-L35,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N35" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B36" s="21" t="str">
+        <f aca="false">TEXT(A36,"yyyy-mm")</f>
+        <v>2026-02</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="H36" s="22" t="n">
+        <f aca="false">IF(J36&gt;0,J36,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <f aca="false">IF(J36&lt;0,-J36,0)</f>
+        <v>1160.58</v>
+      </c>
+      <c r="J36" s="23" t="n">
+        <v>-1160.58</v>
+      </c>
+      <c r="K36" s="22" t="n">
+        <f aca="false">K35+J36</f>
+        <v>2269.78</v>
+      </c>
+      <c r="L36" s="23" t="n">
+        <v>2269.78</v>
+      </c>
+      <c r="M36" s="22" t="n">
+        <f aca="false">ROUND(K36-L36,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B37" s="21" t="str">
+        <f aca="false">TEXT(A37,"yyyy-mm")</f>
+        <v>2026-02</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="H37" s="22" t="n">
+        <f aca="false">IF(J37&gt;0,J37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="22" t="n">
+        <f aca="false">IF(J37&lt;0,-J37,0)</f>
+        <v>2139.83</v>
+      </c>
+      <c r="J37" s="23" t="n">
+        <v>-2139.83</v>
+      </c>
+      <c r="K37" s="22" t="n">
+        <f aca="false">K36+J37</f>
+        <v>129.950000000001</v>
+      </c>
+      <c r="L37" s="23" t="n">
+        <v>129.95</v>
+      </c>
+      <c r="M37" s="22" t="n">
+        <f aca="false">ROUND(K37-L37,2)</f>
+        <v>0</v>
+      </c>
+      <c r="N37" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G38" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="H38" s="25" t="n">
+        <f aca="false">SUM(H2:H37)</f>
+        <v>24332</v>
+      </c>
+      <c r="I38" s="25" t="n">
+        <f aca="false">SUM(I2:I37)</f>
+        <v>24202.05</v>
+      </c>
+      <c r="J38" s="25" t="n">
+        <f aca="false">SUM(J2:J37)</f>
+        <v>129.950000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N37"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="26" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="27" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="B5" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="30" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$H:$H,'Monzo Transactions'!$B:$B,$A5)</f>
+        <v>7682</v>
+      </c>
+      <c r="D5" s="30" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$I:$I,'Monzo Transactions'!$B:$B,$A5)</f>
+        <v>3000</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <f aca="false">B5+C5-D5</f>
+        <v>4682</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <v>4682</v>
+      </c>
+      <c r="G5" s="30" t="n">
+        <f aca="false">ROUND(E5-F5,2)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>7682</v>
+      </c>
+      <c r="I5" s="29" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J5" s="30" t="n">
+        <f aca="false">ROUND((C5-H5)+(D5-I5),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="28" t="str">
+        <f aca="false">IF(AND(G5=0,OR(J5=0,J5="n/a")),"Reconciled","CHECK")</f>
+        <v>Reconciled</v>
+      </c>
+      <c r="L5" s="28" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="B6" s="30" t="n">
+        <f aca="false">F5</f>
+        <v>4682</v>
+      </c>
+      <c r="C6" s="30" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$H:$H,'Monzo Transactions'!$B:$B,$A6)</f>
+        <v>5550</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$I:$I,'Monzo Transactions'!$B:$B,$A6)</f>
+        <v>7800.41</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <f aca="false">B6+C6-D6</f>
+        <v>2431.59</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>2431.59</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <f aca="false">ROUND(E6-F6,2)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>5550</v>
+      </c>
+      <c r="I6" s="29" t="n">
+        <v>7800.41</v>
+      </c>
+      <c r="J6" s="30" t="n">
+        <f aca="false">ROUND((C6-H6)+(D6-I6),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="28" t="str">
+        <f aca="false">IF(AND(G6=0,OR(J6=0,J6="n/a")),"Reconciled","CHECK")</f>
+        <v>Reconciled</v>
+      </c>
+      <c r="L6" s="28" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="B7" s="30" t="n">
+        <f aca="false">F6</f>
+        <v>2431.59</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$H:$H,'Monzo Transactions'!$B:$B,$A7)</f>
+        <v>1000</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$I:$I,'Monzo Transactions'!$B:$B,$A7)</f>
+        <v>3300.41</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <f aca="false">B7+C7-D7</f>
+        <v>131.18</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>131.18</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <f aca="false">ROUND(E7-F7,2)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I7" s="29" t="n">
+        <v>3300.41</v>
+      </c>
+      <c r="J7" s="30" t="n">
+        <f aca="false">ROUND((C7-H7)+(D7-I7),2)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="28" t="str">
+        <f aca="false">IF(AND(G7=0,OR(J7=0,J7="n/a")),"Reconciled","CHECK")</f>
+        <v>Reconciled</v>
+      </c>
+      <c r="L7" s="28" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>252</v>
+      </c>
+      <c r="B8" s="30" t="n">
+        <f aca="false">F7</f>
+        <v>131.18</v>
+      </c>
+      <c r="C8" s="30" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$H:$H,'Monzo Transactions'!$B:$B,$A8)</f>
+        <v>5300</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$I:$I,'Monzo Transactions'!$B:$B,$A8)</f>
+        <v>3500.41</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <f aca="false">B8+C8-D8</f>
+        <v>1930.77</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>1930.77</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <f aca="false">ROUND(E8-F8,2)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="K8" s="28" t="str">
+        <f aca="false">IF(AND(G8=0,OR(J8=0,J8="n/a")),"Reconciled","CHECK")</f>
+        <v>Reconciled</v>
+      </c>
+      <c r="L8" s="28" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="B9" s="30" t="n">
+        <f aca="false">F8</f>
+        <v>1930.77</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$H:$H,'Monzo Transactions'!$B:$B,$A9)</f>
+        <v>2400</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$I:$I,'Monzo Transactions'!$B:$B,$A9)</f>
+        <v>3300.41</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <f aca="false">B9+C9-D9</f>
+        <v>1030.36</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>1030.36</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <f aca="false">ROUND(E9-F9,2)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="K9" s="28" t="str">
+        <f aca="false">IF(AND(G9=0,OR(J9=0,J9="n/a")),"Reconciled","CHECK")</f>
+        <v>Reconciled</v>
+      </c>
+      <c r="L9" s="28" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="s">
+        <v>256</v>
+      </c>
+      <c r="B10" s="30" t="n">
+        <f aca="false">F9</f>
+        <v>1030.36</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$H:$H,'Monzo Transactions'!$B:$B,$A10)</f>
+        <v>2400</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$I:$I,'Monzo Transactions'!$B:$B,$A10)</f>
+        <v>3300.41</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <f aca="false">B10+C10-D10</f>
+        <v>129.95</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <v>129.95</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <f aca="false">ROUND(E10-F10,2)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="K10" s="28" t="str">
+        <f aca="false">IF(AND(G10=0,OR(J10=0,J10="n/a")),"Reconciled","CHECK")</f>
+        <v>Reconciled</v>
+      </c>
+      <c r="L10" s="28" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32" t="n">
+        <f aca="false">SUM(C5:C10)</f>
+        <v>24332</v>
+      </c>
+      <c r="D11" s="32" t="n">
+        <f aca="false">SUM(D5:D10)</f>
+        <v>24202.05</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <f aca="false">B5+C11-D11</f>
+        <v>129.950000000001</v>
+      </c>
+      <c r="F11" s="32" t="n">
+        <f aca="false">F10</f>
+        <v>129.95</v>
+      </c>
+      <c r="G11" s="32" t="n">
+        <f aca="false">ROUND(E11-F11,2)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="D13" s="24" t="n">
+        <f aca="false">COUNTIF('Monzo Transactions'!M2:M37,"&lt;&gt;0")</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="70"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="26" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="27" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="B5" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>2100</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>1900</v>
+      </c>
+      <c r="G5" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="35" t="n">
+        <f aca="false">SUM(B5:G5)</f>
+        <v>4000</v>
+      </c>
+      <c r="I5" s="28" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A5)</f>
+        <v>6</v>
+      </c>
+      <c r="J5" s="36"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>-1000</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>2000</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>200</v>
+      </c>
+      <c r="G6" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>1400</v>
+      </c>
+      <c r="H6" s="35" t="n">
+        <f aca="false">SUM(B6:G6)</f>
+        <v>2600</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A6)</f>
+        <v>4</v>
+      </c>
+      <c r="J6" s="36" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>6400</v>
+      </c>
+      <c r="C7" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>1000</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <f aca="false">SUM(B7:G7)</f>
+        <v>7400</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A7)</f>
+        <v>3</v>
+      </c>
+      <c r="J7" s="36" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>1282</v>
+      </c>
+      <c r="C8" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>5550</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>300</v>
+      </c>
+      <c r="G8" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="35" t="n">
+        <f aca="false">SUM(B8:G8)</f>
+        <v>7132</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A8)</f>
+        <v>6</v>
+      </c>
+      <c r="J8" s="36" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>1000</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>1200</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="35" t="n">
+        <f aca="false">SUM(B9:G9)</f>
+        <v>2200</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A9)</f>
+        <v>3</v>
+      </c>
+      <c r="J9" s="36" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>-3000</v>
+      </c>
+      <c r="C10" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>-1500</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="35" t="n">
+        <f aca="false">SUM(B10:G10)</f>
+        <v>-4500</v>
+      </c>
+      <c r="I10" s="28" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A10)</f>
+        <v>2</v>
+      </c>
+      <c r="J10" s="36"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>-1160.58</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>-1160.58</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>-1160.58</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>-1160.58</v>
+      </c>
+      <c r="G11" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>-1160.58</v>
+      </c>
+      <c r="H11" s="35" t="n">
+        <f aca="false">SUM(B11:G11)</f>
+        <v>-5802.9</v>
+      </c>
+      <c r="I11" s="28" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A11)</f>
+        <v>5</v>
+      </c>
+      <c r="J11" s="36"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="B12" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>-2139.83</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>-2139.83</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>-2139.83</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>-2139.83</v>
+      </c>
+      <c r="G12" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>-2139.83</v>
+      </c>
+      <c r="H12" s="35" t="n">
+        <f aca="false">SUM(B12:G12)</f>
+        <v>-10699.15</v>
+      </c>
+      <c r="I12" s="28" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A12)</f>
+        <v>5</v>
+      </c>
+      <c r="J12" s="36"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>-2000</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>-200</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="34" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="35" t="n">
+        <f aca="false">SUM(B13:G13)</f>
+        <v>-2200</v>
+      </c>
+      <c r="I13" s="28" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A13)</f>
+        <v>2</v>
+      </c>
+      <c r="J13" s="36" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="B14" s="32" t="n">
+        <f aca="false">SUM(B5:B13)</f>
+        <v>4682</v>
+      </c>
+      <c r="C14" s="32" t="n">
+        <f aca="false">SUM(C5:C13)</f>
+        <v>-2250.41</v>
+      </c>
+      <c r="D14" s="32" t="n">
+        <f aca="false">SUM(D5:D13)</f>
+        <v>-2300.41</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <f aca="false">SUM(E5:E13)</f>
+        <v>1799.59</v>
+      </c>
+      <c r="F14" s="32" t="n">
+        <f aca="false">SUM(F5:F13)</f>
+        <v>-900.41</v>
+      </c>
+      <c r="G14" s="32" t="n">
+        <f aca="false">SUM(G5:G13)</f>
+        <v>-900.41</v>
+      </c>
+      <c r="H14" s="32" t="n">
+        <f aca="false">SUM(H5:H13)</f>
+        <v>129.950000000001</v>
+      </c>
+      <c r="I14" s="37" t="n">
+        <f aca="false">SUM(I5:I13)</f>
+        <v>36</v>
+      </c>
+      <c r="J14" s="32"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="B15" s="38" t="n">
+        <f aca="false">ROUND(B14-('Monzo Reconciliation'!C5-'Monzo Reconciliation'!D5),2)</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="38" t="n">
+        <f aca="false">ROUND(C14-('Monzo Reconciliation'!C6-'Monzo Reconciliation'!D6),2)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="38" t="n">
+        <f aca="false">ROUND(D14-('Monzo Reconciliation'!C7-'Monzo Reconciliation'!D7),2)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="38" t="n">
+        <f aca="false">ROUND(E14-('Monzo Reconciliation'!C8-'Monzo Reconciliation'!D8),2)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="38" t="n">
+        <f aca="false">ROUND(F14-('Monzo Reconciliation'!C9-'Monzo Reconciliation'!D9),2)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="38" t="n">
+        <f aca="false">ROUND(G14-('Monzo Reconciliation'!C10-'Monzo Reconciliation'!D10),2)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/data/rent_split.xlsx
+++ b/data/rent_split.xlsx
@@ -13,8 +13,11 @@
     <sheet name="Monzo Transactions" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Monzo Reconciliation" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Monzo Categories" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Completion Lines" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Property Purchase" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Completion Lines'!$A$1:$G$41</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Monzo Transactions'!$A$1:$N$37</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Transactions!$A$1:$F$100</definedName>
   </definedNames>
@@ -95,8 +98,30 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">My accounting classification. Edit freely – Property Purchase sheet uses SUMIFS on this column.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="368">
   <si>
     <t xml:space="preserve">Rent Split – Total per Property</t>
   </si>
@@ -903,19 +928,317 @@
   </si>
   <si>
     <t xml:space="preserve">Check vs reconciliation (should be 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid In (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid Out – net (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAT (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid Out – gross (£)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 Strensall Rd – Remortgage (17/07/2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortgage advance minus 3rd party solicitors fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding – Strensall remortgage advance (net)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money on account 8.4.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding – money on account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal Fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finance cost – Strensall remortgage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">File Setup Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortgage Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third party sols fee for dealing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Searches Indemnity Insurance Policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land Charges Search (£6 per person) x 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Transfer Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land Registry Documents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land Registry Search – OS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land Registry Fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MR01 Companies House registration of charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company winding up search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company search – Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance due on completion → sent to Cairnsford purchase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transfer – Strensall proceeds to Cairnsford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36 Cairnsford Rd – Purchase (17/07/2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchase Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property cost – purchase price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money on Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortgage advance from lender's solicitors (net of their fees)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding – Together Commercial mortgage (net)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proceeds from 30 Strensall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money from client – Alvine 14.7.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding – Alvine Tchega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money from client – Kakmeni 14.7.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funding – Kakmeni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property cost – legal &amp; acquisition fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortgage Admin Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finance cost – Cairnsford mortgage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stamp Duty Land Tax Form Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anti-Money Laundering Check Fee (£30 pp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third party lender solicitors fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policy arrangement fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land Registry Search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land Charges Search (£6 pp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Searches Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stamp Duty (SDLT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property cost – Stamp Duty (SDLT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search perusal Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company search fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MR01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winding up Search Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insolvency indemnity policy required by lender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check against statement totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid In – calc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid In – statement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid Out – calc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paid Out – statement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF: CompletionStatement_1093081_Tchega_2025-07-15 (total out £1,670 + balance due £131,958)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDF: Complation_Statement (DWS Legal), totals £500,658.94 / £500,658.94, balance £0.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36 Cairnsford Road, Leicester LE2 6GF – Purchase Analysis (Alino Property Ltd)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed 17/07/2025, funded partly by remortgage of 30 Strensall Road. All figures are SUMIFS over Completion Lines (gross incl. VAT – treated as irrecoverable).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Cost of property (capitalise – fixed asset / investment property)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">£</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchase price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stamp Duty Land Tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDLT is part of the cost of the property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal &amp; acquisition fees (incl. VAT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal, searches, Land Registry, AML, SDLT form, bank transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total cost of 36 Cairnsford Road</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. Finance / loan arrangement costs (not property cost)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cairnsford mortgage – lender-related fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mortgage admin, lender sols, policy arrangement, insolvency indemnity, MR01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 Strensall remortgage – all costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole remortgage statement (£1,670); spread over loan term or expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total finance costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C. How the purchase was funded (Cairnsford statement – paid in)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Together Commercial mortgage (net advance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net of lender's solicitor fees; gross loan not shown on statement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proceeds of 30 Strensall remortgage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equals £133,528 advance + £100 on account − £1,670 costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvine Tchega – money in 14/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director's loan to company (confirm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kakmeni – money in 14/07/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan or investment? Ties to Kakmeni receipts on Monzo (confirm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Money on account (Cairnsford)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total funds in for purchase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost (A) + Cairnsford finance fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funds in (C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference (should be 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E. Ongoing mortgage payments (from Monzo business account)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Together Commercial DD 10395974-002 – paid Oct-25 to Feb-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likely the larger Cairnsford loan (confirm with Together)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Together Commercial DD 10395973-002 – paid Oct-25 to Feb-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Likely the 30 Strensall remortgage (confirm with Together)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
     <numFmt numFmtId="166" formatCode="\£#,##0.00;&quot;(£&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="168" formatCode="\£#,##0.00;&quot;-£&quot;#,##0.00;\-"/>
     <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="\£#,##0.00;&quot;-£&quot;#,##0.00;\-"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -1078,7 +1401,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="46">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1159,7 +1482,51 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1167,11 +1534,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1179,7 +1546,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1187,19 +1562,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1207,31 +1578,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1345,6 +1696,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -4024,17 +4379,17 @@
   <dimension ref="A1:N38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4081,1783 +4436,1783 @@
         <v>183</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="n">
         <v>45919</v>
       </c>
-      <c r="B2" s="21" t="str">
+      <c r="B2" s="16" t="str">
         <f aca="false">TEXT(A2,"yyyy-mm")</f>
         <v>2025-09</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="H2" s="22" t="n">
+      <c r="H2" s="20" t="n">
         <f aca="false">IF(J2&gt;0,J2,0)</f>
         <v>5000</v>
       </c>
-      <c r="I2" s="22" t="n">
+      <c r="I2" s="20" t="n">
         <f aca="false">IF(J2&lt;0,-J2,0)</f>
         <v>0</v>
       </c>
-      <c r="J2" s="23" t="n">
+      <c r="J2" s="21" t="n">
         <v>5000</v>
       </c>
-      <c r="K2" s="22" t="n">
+      <c r="K2" s="20" t="n">
         <f aca="false">J2</f>
         <v>5000</v>
       </c>
-      <c r="L2" s="23" t="n">
+      <c r="L2" s="21" t="n">
         <v>5000</v>
       </c>
-      <c r="M2" s="22" t="n">
+      <c r="M2" s="20" t="n">
         <f aca="false">ROUND(K2-L2,2)</f>
         <v>0</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="N2" s="16" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="n">
         <v>45919</v>
       </c>
-      <c r="B3" s="21" t="str">
+      <c r="B3" s="16" t="str">
         <f aca="false">TEXT(A3,"yyyy-mm")</f>
         <v>2025-09</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="H3" s="22" t="n">
+      <c r="H3" s="20" t="n">
         <f aca="false">IF(J3&gt;0,J3,0)</f>
         <v>1400</v>
       </c>
-      <c r="I3" s="22" t="n">
+      <c r="I3" s="20" t="n">
         <f aca="false">IF(J3&lt;0,-J3,0)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="23" t="n">
+      <c r="J3" s="21" t="n">
         <v>1400</v>
       </c>
-      <c r="K3" s="22" t="n">
+      <c r="K3" s="20" t="n">
         <f aca="false">K2+J3</f>
         <v>6400</v>
       </c>
-      <c r="L3" s="23" t="n">
+      <c r="L3" s="21" t="n">
         <v>6400</v>
       </c>
-      <c r="M3" s="22" t="n">
+      <c r="M3" s="20" t="n">
         <f aca="false">ROUND(K3-L3,2)</f>
         <v>0</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="N3" s="16" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="n">
         <v>45921</v>
       </c>
-      <c r="B4" s="21" t="str">
+      <c r="B4" s="16" t="str">
         <f aca="false">TEXT(A4,"yyyy-mm")</f>
         <v>2025-09</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="H4" s="22" t="n">
+      <c r="H4" s="20" t="n">
         <f aca="false">IF(J4&gt;0,J4,0)</f>
         <v>1282</v>
       </c>
-      <c r="I4" s="22" t="n">
+      <c r="I4" s="20" t="n">
         <f aca="false">IF(J4&lt;0,-J4,0)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="23" t="n">
+      <c r="J4" s="21" t="n">
         <v>1282</v>
       </c>
-      <c r="K4" s="22" t="n">
+      <c r="K4" s="20" t="n">
         <f aca="false">K3+J4</f>
         <v>7682</v>
       </c>
-      <c r="L4" s="23" t="n">
+      <c r="L4" s="21" t="n">
         <v>7682</v>
       </c>
-      <c r="M4" s="22" t="n">
+      <c r="M4" s="20" t="n">
         <f aca="false">ROUND(K4-L4,2)</f>
         <v>0</v>
       </c>
-      <c r="N4" s="21" t="s">
+      <c r="N4" s="16" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="n">
         <v>45922</v>
       </c>
-      <c r="B5" s="21" t="str">
+      <c r="B5" s="16" t="str">
         <f aca="false">TEXT(A5,"yyyy-mm")</f>
         <v>2025-09</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="20" t="n">
         <f aca="false">IF(J5&gt;0,J5,0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="22" t="n">
+      <c r="I5" s="20" t="n">
         <f aca="false">IF(J5&lt;0,-J5,0)</f>
         <v>3000</v>
       </c>
-      <c r="J5" s="23" t="n">
+      <c r="J5" s="21" t="n">
         <v>-3000</v>
       </c>
-      <c r="K5" s="22" t="n">
+      <c r="K5" s="20" t="n">
         <f aca="false">K4+J5</f>
         <v>4682</v>
       </c>
-      <c r="L5" s="23" t="n">
+      <c r="L5" s="21" t="n">
         <v>4682</v>
       </c>
-      <c r="M5" s="22" t="n">
+      <c r="M5" s="20" t="n">
         <f aca="false">ROUND(K5-L5,2)</f>
         <v>0</v>
       </c>
-      <c r="N5" s="21" t="s">
+      <c r="N5" s="16" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="n">
         <v>45931</v>
       </c>
-      <c r="B6" s="21" t="str">
+      <c r="B6" s="16" t="str">
         <f aca="false">TEXT(A6,"yyyy-mm")</f>
         <v>2025-10</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="20" t="n">
         <f aca="false">IF(J6&gt;0,J6,0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="20" t="n">
         <f aca="false">IF(J6&lt;0,-J6,0)</f>
         <v>1500</v>
       </c>
-      <c r="J6" s="23" t="n">
+      <c r="J6" s="21" t="n">
         <v>-1500</v>
       </c>
-      <c r="K6" s="22" t="n">
+      <c r="K6" s="20" t="n">
         <f aca="false">K5+J6</f>
         <v>3182</v>
       </c>
-      <c r="L6" s="23" t="n">
+      <c r="L6" s="21" t="n">
         <v>3182</v>
       </c>
-      <c r="M6" s="22" t="n">
+      <c r="M6" s="20" t="n">
         <f aca="false">ROUND(K6-L6,2)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="21" t="s">
+      <c r="N6" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="n">
         <v>45936</v>
       </c>
-      <c r="B7" s="21" t="str">
+      <c r="B7" s="16" t="str">
         <f aca="false">TEXT(A7,"yyyy-mm")</f>
         <v>2025-10</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="20" t="n">
         <f aca="false">IF(J7&gt;0,J7,0)</f>
         <v>1300</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="20" t="n">
         <f aca="false">IF(J7&lt;0,-J7,0)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="23" t="n">
+      <c r="J7" s="21" t="n">
         <v>1300</v>
       </c>
-      <c r="K7" s="22" t="n">
+      <c r="K7" s="20" t="n">
         <f aca="false">K6+J7</f>
         <v>4482</v>
       </c>
-      <c r="L7" s="23" t="n">
+      <c r="L7" s="21" t="n">
         <v>4482</v>
       </c>
-      <c r="M7" s="22" t="n">
+      <c r="M7" s="20" t="n">
         <f aca="false">ROUND(K7-L7,2)</f>
         <v>0</v>
       </c>
-      <c r="N7" s="21" t="s">
+      <c r="N7" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="n">
         <v>45936</v>
       </c>
-      <c r="B8" s="21" t="str">
+      <c r="B8" s="16" t="str">
         <f aca="false">TEXT(A8,"yyyy-mm")</f>
         <v>2025-10</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="20" t="n">
         <f aca="false">IF(J8&gt;0,J8,0)</f>
         <v>1250</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="20" t="n">
         <f aca="false">IF(J8&lt;0,-J8,0)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="23" t="n">
+      <c r="J8" s="21" t="n">
         <v>1250</v>
       </c>
-      <c r="K8" s="22" t="n">
+      <c r="K8" s="20" t="n">
         <f aca="false">K7+J8</f>
         <v>5732</v>
       </c>
-      <c r="L8" s="23" t="n">
+      <c r="L8" s="21" t="n">
         <v>5732</v>
       </c>
-      <c r="M8" s="22" t="n">
+      <c r="M8" s="20" t="n">
         <f aca="false">ROUND(K8-L8,2)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="21" t="s">
+      <c r="N8" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15" t="n">
         <v>45936</v>
       </c>
-      <c r="B9" s="21" t="str">
+      <c r="B9" s="16" t="str">
         <f aca="false">TEXT(A9,"yyyy-mm")</f>
         <v>2025-10</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="H9" s="22" t="n">
+      <c r="H9" s="20" t="n">
         <f aca="false">IF(J9&gt;0,J9,0)</f>
         <v>500</v>
       </c>
-      <c r="I9" s="22" t="n">
+      <c r="I9" s="20" t="n">
         <f aca="false">IF(J9&lt;0,-J9,0)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="23" t="n">
+      <c r="J9" s="21" t="n">
         <v>500</v>
       </c>
-      <c r="K9" s="22" t="n">
+      <c r="K9" s="20" t="n">
         <f aca="false">K8+J9</f>
         <v>6232</v>
       </c>
-      <c r="L9" s="23" t="n">
+      <c r="L9" s="21" t="n">
         <v>6232</v>
       </c>
-      <c r="M9" s="22" t="n">
+      <c r="M9" s="20" t="n">
         <f aca="false">ROUND(K9-L9,2)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="21" t="s">
+      <c r="N9" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15" t="n">
         <v>45937</v>
       </c>
-      <c r="B10" s="21" t="str">
+      <c r="B10" s="16" t="str">
         <f aca="false">TEXT(A10,"yyyy-mm")</f>
         <v>2025-10</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="H10" s="22" t="n">
+      <c r="H10" s="20" t="n">
         <f aca="false">IF(J10&gt;0,J10,0)</f>
         <v>2500</v>
       </c>
-      <c r="I10" s="22" t="n">
+      <c r="I10" s="20" t="n">
         <f aca="false">IF(J10&lt;0,-J10,0)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="23" t="n">
+      <c r="J10" s="21" t="n">
         <v>2500</v>
       </c>
-      <c r="K10" s="22" t="n">
+      <c r="K10" s="20" t="n">
         <f aca="false">K9+J10</f>
         <v>8732</v>
       </c>
-      <c r="L10" s="23" t="n">
+      <c r="L10" s="21" t="n">
         <v>8732</v>
       </c>
-      <c r="M10" s="22" t="n">
+      <c r="M10" s="20" t="n">
         <f aca="false">ROUND(K10-L10,2)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="21" t="s">
+      <c r="N10" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="n">
         <v>45944</v>
       </c>
-      <c r="B11" s="21" t="str">
+      <c r="B11" s="16" t="str">
         <f aca="false">TEXT(A11,"yyyy-mm")</f>
         <v>2025-10</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="H11" s="22" t="n">
+      <c r="H11" s="20" t="n">
         <f aca="false">IF(J11&gt;0,J11,0)</f>
         <v>0</v>
       </c>
-      <c r="I11" s="22" t="n">
+      <c r="I11" s="20" t="n">
         <f aca="false">IF(J11&lt;0,-J11,0)</f>
         <v>1000</v>
       </c>
-      <c r="J11" s="23" t="n">
+      <c r="J11" s="21" t="n">
         <v>-1000</v>
       </c>
-      <c r="K11" s="22" t="n">
+      <c r="K11" s="20" t="n">
         <f aca="false">K10+J11</f>
         <v>7732</v>
       </c>
-      <c r="L11" s="23" t="n">
+      <c r="L11" s="21" t="n">
         <v>7732</v>
       </c>
-      <c r="M11" s="22" t="n">
+      <c r="M11" s="20" t="n">
         <f aca="false">ROUND(K11-L11,2)</f>
         <v>0</v>
       </c>
-      <c r="N11" s="21" t="s">
+      <c r="N11" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="n">
         <v>45944</v>
       </c>
-      <c r="B12" s="21" t="str">
+      <c r="B12" s="16" t="str">
         <f aca="false">TEXT(A12,"yyyy-mm")</f>
         <v>2025-10</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="H12" s="22" t="n">
+      <c r="H12" s="20" t="n">
         <f aca="false">IF(J12&gt;0,J12,0)</f>
         <v>0</v>
       </c>
-      <c r="I12" s="22" t="n">
+      <c r="I12" s="20" t="n">
         <f aca="false">IF(J12&lt;0,-J12,0)</f>
         <v>2000</v>
       </c>
-      <c r="J12" s="23" t="n">
+      <c r="J12" s="21" t="n">
         <v>-2000</v>
       </c>
-      <c r="K12" s="22" t="n">
+      <c r="K12" s="20" t="n">
         <f aca="false">K11+J12</f>
         <v>5732</v>
       </c>
-      <c r="L12" s="23" t="n">
+      <c r="L12" s="21" t="n">
         <v>5732</v>
       </c>
-      <c r="M12" s="22" t="n">
+      <c r="M12" s="20" t="n">
         <f aca="false">ROUND(K12-L12,2)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="21" t="s">
+      <c r="N12" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="n">
         <v>45947</v>
       </c>
-      <c r="B13" s="21" t="str">
+      <c r="B13" s="16" t="str">
         <f aca="false">TEXT(A13,"yyyy-mm")</f>
         <v>2025-10</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="G13" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="H13" s="22" t="n">
+      <c r="H13" s="20" t="n">
         <f aca="false">IF(J13&gt;0,J13,0)</f>
         <v>0</v>
       </c>
-      <c r="I13" s="22" t="n">
+      <c r="I13" s="20" t="n">
         <f aca="false">IF(J13&lt;0,-J13,0)</f>
         <v>2139.83</v>
       </c>
-      <c r="J13" s="23" t="n">
+      <c r="J13" s="21" t="n">
         <v>-2139.83</v>
       </c>
-      <c r="K13" s="22" t="n">
+      <c r="K13" s="20" t="n">
         <f aca="false">K12+J13</f>
         <v>3592.17</v>
       </c>
-      <c r="L13" s="23" t="n">
+      <c r="L13" s="21" t="n">
         <v>3592.17</v>
       </c>
-      <c r="M13" s="22" t="n">
+      <c r="M13" s="20" t="n">
         <f aca="false">ROUND(K13-L13,2)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="21" t="s">
+      <c r="N13" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="n">
         <v>45947</v>
       </c>
-      <c r="B14" s="21" t="str">
+      <c r="B14" s="16" t="str">
         <f aca="false">TEXT(A14,"yyyy-mm")</f>
         <v>2025-10</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="20" t="n">
         <f aca="false">IF(J14&gt;0,J14,0)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="22" t="n">
+      <c r="I14" s="20" t="n">
         <f aca="false">IF(J14&lt;0,-J14,0)</f>
         <v>1160.58</v>
       </c>
-      <c r="J14" s="23" t="n">
+      <c r="J14" s="21" t="n">
         <v>-1160.58</v>
       </c>
-      <c r="K14" s="22" t="n">
+      <c r="K14" s="20" t="n">
         <f aca="false">K13+J14</f>
         <v>2431.59</v>
       </c>
-      <c r="L14" s="23" t="n">
+      <c r="L14" s="21" t="n">
         <v>2431.59</v>
       </c>
-      <c r="M14" s="22" t="n">
+      <c r="M14" s="20" t="n">
         <f aca="false">ROUND(K14-L14,2)</f>
         <v>0</v>
       </c>
-      <c r="N14" s="21" t="s">
+      <c r="N14" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="n">
         <v>45972</v>
       </c>
-      <c r="B15" s="21" t="str">
+      <c r="B15" s="16" t="str">
         <f aca="false">TEXT(A15,"yyyy-mm")</f>
         <v>2025-11</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G15" s="21" t="s">
+      <c r="G15" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="H15" s="22" t="n">
+      <c r="H15" s="20" t="n">
         <f aca="false">IF(J15&gt;0,J15,0)</f>
         <v>1000</v>
       </c>
-      <c r="I15" s="22" t="n">
+      <c r="I15" s="20" t="n">
         <f aca="false">IF(J15&lt;0,-J15,0)</f>
         <v>0</v>
       </c>
-      <c r="J15" s="23" t="n">
+      <c r="J15" s="21" t="n">
         <v>1000</v>
       </c>
-      <c r="K15" s="22" t="n">
+      <c r="K15" s="20" t="n">
         <f aca="false">K14+J15</f>
         <v>3431.59</v>
       </c>
-      <c r="L15" s="23" t="n">
+      <c r="L15" s="21" t="n">
         <v>3431.59</v>
       </c>
-      <c r="M15" s="22" t="n">
+      <c r="M15" s="20" t="n">
         <f aca="false">ROUND(K15-L15,2)</f>
         <v>0</v>
       </c>
-      <c r="N15" s="21" t="s">
+      <c r="N15" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="n">
         <v>45978</v>
       </c>
-      <c r="B16" s="21" t="str">
+      <c r="B16" s="16" t="str">
         <f aca="false">TEXT(A16,"yyyy-mm")</f>
         <v>2025-11</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="20" t="n">
         <f aca="false">IF(J16&gt;0,J16,0)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="22" t="n">
+      <c r="I16" s="20" t="n">
         <f aca="false">IF(J16&lt;0,-J16,0)</f>
         <v>2139.83</v>
       </c>
-      <c r="J16" s="23" t="n">
+      <c r="J16" s="21" t="n">
         <v>-2139.83</v>
       </c>
-      <c r="K16" s="22" t="n">
+      <c r="K16" s="20" t="n">
         <f aca="false">K15+J16</f>
         <v>1291.76</v>
       </c>
-      <c r="L16" s="23" t="n">
+      <c r="L16" s="21" t="n">
         <v>1291.76</v>
       </c>
-      <c r="M16" s="22" t="n">
+      <c r="M16" s="20" t="n">
         <f aca="false">ROUND(K16-L16,2)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="21" t="s">
+      <c r="N16" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="n">
         <v>45978</v>
       </c>
-      <c r="B17" s="21" t="str">
+      <c r="B17" s="16" t="str">
         <f aca="false">TEXT(A17,"yyyy-mm")</f>
         <v>2025-11</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="H17" s="22" t="n">
+      <c r="H17" s="20" t="n">
         <f aca="false">IF(J17&gt;0,J17,0)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="22" t="n">
+      <c r="I17" s="20" t="n">
         <f aca="false">IF(J17&lt;0,-J17,0)</f>
         <v>1160.58</v>
       </c>
-      <c r="J17" s="23" t="n">
+      <c r="J17" s="21" t="n">
         <v>-1160.58</v>
       </c>
-      <c r="K17" s="22" t="n">
+      <c r="K17" s="20" t="n">
         <f aca="false">K16+J17</f>
         <v>131.18</v>
       </c>
-      <c r="L17" s="23" t="n">
+      <c r="L17" s="21" t="n">
         <v>131.18</v>
       </c>
-      <c r="M17" s="22" t="n">
+      <c r="M17" s="20" t="n">
         <f aca="false">ROUND(K17-L17,2)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="21" t="s">
+      <c r="N17" s="16" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="n">
         <v>46007</v>
       </c>
-      <c r="B18" s="21" t="str">
+      <c r="B18" s="16" t="str">
         <f aca="false">TEXT(A18,"yyyy-mm")</f>
         <v>2025-12</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="H18" s="22" t="n">
+      <c r="H18" s="20" t="n">
         <f aca="false">IF(J18&gt;0,J18,0)</f>
         <v>2000</v>
       </c>
-      <c r="I18" s="22" t="n">
+      <c r="I18" s="20" t="n">
         <f aca="false">IF(J18&lt;0,-J18,0)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="23" t="n">
+      <c r="J18" s="21" t="n">
         <v>2000</v>
       </c>
-      <c r="K18" s="22" t="n">
+      <c r="K18" s="20" t="n">
         <f aca="false">K17+J18</f>
         <v>2131.18</v>
       </c>
-      <c r="L18" s="23" t="n">
+      <c r="L18" s="21" t="n">
         <v>2131.18</v>
       </c>
-      <c r="M18" s="22" t="n">
+      <c r="M18" s="20" t="n">
         <f aca="false">ROUND(K18-L18,2)</f>
         <v>0</v>
       </c>
-      <c r="N18" s="21" t="s">
+      <c r="N18" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="15" t="n">
         <v>46007</v>
       </c>
-      <c r="B19" s="21" t="str">
+      <c r="B19" s="16" t="str">
         <f aca="false">TEXT(A19,"yyyy-mm")</f>
         <v>2025-12</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G19" s="21" t="s">
+      <c r="G19" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="H19" s="22" t="n">
+      <c r="H19" s="20" t="n">
         <f aca="false">IF(J19&gt;0,J19,0)</f>
         <v>1100</v>
       </c>
-      <c r="I19" s="22" t="n">
+      <c r="I19" s="20" t="n">
         <f aca="false">IF(J19&lt;0,-J19,0)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="23" t="n">
+      <c r="J19" s="21" t="n">
         <v>1100</v>
       </c>
-      <c r="K19" s="22" t="n">
+      <c r="K19" s="20" t="n">
         <f aca="false">K18+J19</f>
         <v>3231.18</v>
       </c>
-      <c r="L19" s="23" t="n">
+      <c r="L19" s="21" t="n">
         <v>3231.18</v>
       </c>
-      <c r="M19" s="22" t="n">
+      <c r="M19" s="20" t="n">
         <f aca="false">ROUND(K19-L19,2)</f>
         <v>0</v>
       </c>
-      <c r="N19" s="21" t="s">
+      <c r="N19" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="n">
         <v>46007</v>
       </c>
-      <c r="B20" s="21" t="str">
+      <c r="B20" s="16" t="str">
         <f aca="false">TEXT(A20,"yyyy-mm")</f>
         <v>2025-12</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G20" s="21" t="s">
+      <c r="G20" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="H20" s="22" t="n">
+      <c r="H20" s="20" t="n">
         <f aca="false">IF(J20&gt;0,J20,0)</f>
         <v>100</v>
       </c>
-      <c r="I20" s="22" t="n">
+      <c r="I20" s="20" t="n">
         <f aca="false">IF(J20&lt;0,-J20,0)</f>
         <v>0</v>
       </c>
-      <c r="J20" s="23" t="n">
+      <c r="J20" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="K20" s="22" t="n">
+      <c r="K20" s="20" t="n">
         <f aca="false">K19+J20</f>
         <v>3331.18</v>
       </c>
-      <c r="L20" s="23" t="n">
+      <c r="L20" s="21" t="n">
         <v>3331.18</v>
       </c>
-      <c r="M20" s="22" t="n">
+      <c r="M20" s="20" t="n">
         <f aca="false">ROUND(K20-L20,2)</f>
         <v>0</v>
       </c>
-      <c r="N20" s="21" t="s">
+      <c r="N20" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="n">
         <v>46008</v>
       </c>
-      <c r="B21" s="21" t="str">
+      <c r="B21" s="16" t="str">
         <f aca="false">TEXT(A21,"yyyy-mm")</f>
         <v>2025-12</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="G21" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="H21" s="22" t="n">
+      <c r="H21" s="20" t="n">
         <f aca="false">IF(J21&gt;0,J21,0)</f>
         <v>0</v>
       </c>
-      <c r="I21" s="22" t="n">
+      <c r="I21" s="20" t="n">
         <f aca="false">IF(J21&lt;0,-J21,0)</f>
         <v>1160.58</v>
       </c>
-      <c r="J21" s="23" t="n">
+      <c r="J21" s="21" t="n">
         <v>-1160.58</v>
       </c>
-      <c r="K21" s="22" t="n">
+      <c r="K21" s="20" t="n">
         <f aca="false">K20+J21</f>
         <v>2170.6</v>
       </c>
-      <c r="L21" s="23" t="n">
+      <c r="L21" s="21" t="n">
         <v>2170.6</v>
       </c>
-      <c r="M21" s="22" t="n">
+      <c r="M21" s="20" t="n">
         <f aca="false">ROUND(K21-L21,2)</f>
         <v>0</v>
       </c>
-      <c r="N21" s="21" t="s">
+      <c r="N21" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="15" t="n">
         <v>46008</v>
       </c>
-      <c r="B22" s="21" t="str">
+      <c r="B22" s="16" t="str">
         <f aca="false">TEXT(A22,"yyyy-mm")</f>
         <v>2025-12</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="F22" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G22" s="21" t="s">
+      <c r="G22" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="H22" s="22" t="n">
+      <c r="H22" s="20" t="n">
         <f aca="false">IF(J22&gt;0,J22,0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="22" t="n">
+      <c r="I22" s="20" t="n">
         <f aca="false">IF(J22&lt;0,-J22,0)</f>
         <v>2139.83</v>
       </c>
-      <c r="J22" s="23" t="n">
+      <c r="J22" s="21" t="n">
         <v>-2139.83</v>
       </c>
-      <c r="K22" s="22" t="n">
+      <c r="K22" s="20" t="n">
         <f aca="false">K21+J22</f>
         <v>30.7700000000004</v>
       </c>
-      <c r="L22" s="23" t="n">
+      <c r="L22" s="21" t="n">
         <v>30.77</v>
       </c>
-      <c r="M22" s="22" t="n">
+      <c r="M22" s="20" t="n">
         <f aca="false">ROUND(K22-L22,2)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="21" t="s">
+      <c r="N22" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="15" t="n">
         <v>46008</v>
       </c>
-      <c r="B23" s="21" t="str">
+      <c r="B23" s="16" t="str">
         <f aca="false">TEXT(A23,"yyyy-mm")</f>
         <v>2025-12</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="F23" s="21" t="s">
+      <c r="F23" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G23" s="21" t="s">
+      <c r="G23" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="H23" s="22" t="n">
+      <c r="H23" s="20" t="n">
         <f aca="false">IF(J23&gt;0,J23,0)</f>
         <v>800</v>
       </c>
-      <c r="I23" s="22" t="n">
+      <c r="I23" s="20" t="n">
         <f aca="false">IF(J23&lt;0,-J23,0)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="23" t="n">
+      <c r="J23" s="21" t="n">
         <v>800</v>
       </c>
-      <c r="K23" s="22" t="n">
+      <c r="K23" s="20" t="n">
         <f aca="false">K22+J23</f>
         <v>830.77</v>
       </c>
-      <c r="L23" s="23" t="n">
+      <c r="L23" s="21" t="n">
         <v>830.77</v>
       </c>
-      <c r="M23" s="22" t="n">
+      <c r="M23" s="20" t="n">
         <f aca="false">ROUND(K23-L23,2)</f>
         <v>0</v>
       </c>
-      <c r="N23" s="21" t="s">
+      <c r="N23" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="n">
         <v>46015</v>
       </c>
-      <c r="B24" s="21" t="str">
+      <c r="B24" s="16" t="str">
         <f aca="false">TEXT(A24,"yyyy-mm")</f>
         <v>2025-12</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="F24" s="21" t="s">
+      <c r="F24" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G24" s="21" t="s">
+      <c r="G24" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="H24" s="22" t="n">
+      <c r="H24" s="20" t="n">
         <f aca="false">IF(J24&gt;0,J24,0)</f>
         <v>500</v>
       </c>
-      <c r="I24" s="22" t="n">
+      <c r="I24" s="20" t="n">
         <f aca="false">IF(J24&lt;0,-J24,0)</f>
         <v>0</v>
       </c>
-      <c r="J24" s="23" t="n">
+      <c r="J24" s="21" t="n">
         <v>500</v>
       </c>
-      <c r="K24" s="22" t="n">
+      <c r="K24" s="20" t="n">
         <f aca="false">K23+J24</f>
         <v>1330.77</v>
       </c>
-      <c r="L24" s="23" t="n">
+      <c r="L24" s="21" t="n">
         <v>1330.77</v>
       </c>
-      <c r="M24" s="22" t="n">
+      <c r="M24" s="20" t="n">
         <f aca="false">ROUND(K24-L24,2)</f>
         <v>0</v>
       </c>
-      <c r="N24" s="21" t="s">
+      <c r="N24" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="n">
         <v>46015</v>
       </c>
-      <c r="B25" s="21" t="str">
+      <c r="B25" s="16" t="str">
         <f aca="false">TEXT(A25,"yyyy-mm")</f>
         <v>2025-12</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D25" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="E25" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="F25" s="21" t="s">
+      <c r="F25" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G25" s="21" t="s">
+      <c r="G25" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="H25" s="22" t="n">
+      <c r="H25" s="20" t="n">
         <f aca="false">IF(J25&gt;0,J25,0)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="22" t="n">
+      <c r="I25" s="20" t="n">
         <f aca="false">IF(J25&lt;0,-J25,0)</f>
         <v>200</v>
       </c>
-      <c r="J25" s="23" t="n">
+      <c r="J25" s="21" t="n">
         <v>-200</v>
       </c>
-      <c r="K25" s="22" t="n">
+      <c r="K25" s="20" t="n">
         <f aca="false">K24+J25</f>
         <v>1130.77</v>
       </c>
-      <c r="L25" s="23" t="n">
+      <c r="L25" s="21" t="n">
         <v>1130.77</v>
       </c>
-      <c r="M25" s="22" t="n">
+      <c r="M25" s="20" t="n">
         <f aca="false">ROUND(K25-L25,2)</f>
         <v>0</v>
       </c>
-      <c r="N25" s="21" t="s">
+      <c r="N25" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="n">
         <v>46021</v>
       </c>
-      <c r="B26" s="21" t="str">
+      <c r="B26" s="16" t="str">
         <f aca="false">TEXT(A26,"yyyy-mm")</f>
         <v>2025-12</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="D26" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="E26" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="F26" s="21" t="s">
+      <c r="F26" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G26" s="21" t="s">
+      <c r="G26" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="H26" s="22" t="n">
+      <c r="H26" s="20" t="n">
         <f aca="false">IF(J26&gt;0,J26,0)</f>
         <v>800</v>
       </c>
-      <c r="I26" s="22" t="n">
+      <c r="I26" s="20" t="n">
         <f aca="false">IF(J26&lt;0,-J26,0)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="23" t="n">
+      <c r="J26" s="21" t="n">
         <v>800</v>
       </c>
-      <c r="K26" s="22" t="n">
+      <c r="K26" s="20" t="n">
         <f aca="false">K25+J26</f>
         <v>1930.77</v>
       </c>
-      <c r="L26" s="23" t="n">
+      <c r="L26" s="21" t="n">
         <v>1930.77</v>
       </c>
-      <c r="M26" s="22" t="n">
+      <c r="M26" s="20" t="n">
         <f aca="false">ROUND(K26-L26,2)</f>
         <v>0</v>
       </c>
-      <c r="N26" s="21" t="s">
+      <c r="N26" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15" t="n">
         <v>46028</v>
       </c>
-      <c r="B27" s="21" t="str">
+      <c r="B27" s="16" t="str">
         <f aca="false">TEXT(A27,"yyyy-mm")</f>
         <v>2026-01</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="F27" s="21" t="s">
+      <c r="F27" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G27" s="21" t="s">
+      <c r="G27" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="H27" s="22" t="n">
+      <c r="H27" s="20" t="n">
         <f aca="false">IF(J27&gt;0,J27,0)</f>
         <v>900</v>
       </c>
-      <c r="I27" s="22" t="n">
+      <c r="I27" s="20" t="n">
         <f aca="false">IF(J27&lt;0,-J27,0)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="23" t="n">
+      <c r="J27" s="21" t="n">
         <v>900</v>
       </c>
-      <c r="K27" s="22" t="n">
+      <c r="K27" s="20" t="n">
         <f aca="false">K26+J27</f>
         <v>2830.77</v>
       </c>
-      <c r="L27" s="23" t="n">
+      <c r="L27" s="21" t="n">
         <v>2830.77</v>
       </c>
-      <c r="M27" s="22" t="n">
+      <c r="M27" s="20" t="n">
         <f aca="false">ROUND(K27-L27,2)</f>
         <v>0</v>
       </c>
-      <c r="N27" s="21" t="s">
+      <c r="N27" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="n">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="n">
         <v>46038</v>
       </c>
-      <c r="B28" s="21" t="str">
+      <c r="B28" s="16" t="str">
         <f aca="false">TEXT(A28,"yyyy-mm")</f>
         <v>2026-01</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="D28" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="E28" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="F28" s="21" t="s">
+      <c r="F28" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="21" t="s">
+      <c r="G28" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="H28" s="22" t="n">
+      <c r="H28" s="20" t="n">
         <f aca="false">IF(J28&gt;0,J28,0)</f>
         <v>400</v>
       </c>
-      <c r="I28" s="22" t="n">
+      <c r="I28" s="20" t="n">
         <f aca="false">IF(J28&lt;0,-J28,0)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="23" t="n">
+      <c r="J28" s="21" t="n">
         <v>400</v>
       </c>
-      <c r="K28" s="22" t="n">
+      <c r="K28" s="20" t="n">
         <f aca="false">K27+J28</f>
         <v>3230.77</v>
       </c>
-      <c r="L28" s="23" t="n">
+      <c r="L28" s="21" t="n">
         <v>3230.77</v>
       </c>
-      <c r="M28" s="22" t="n">
+      <c r="M28" s="20" t="n">
         <f aca="false">ROUND(K28-L28,2)</f>
         <v>0</v>
       </c>
-      <c r="N28" s="21" t="s">
+      <c r="N28" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15" t="n">
         <v>46038</v>
       </c>
-      <c r="B29" s="21" t="str">
+      <c r="B29" s="16" t="str">
         <f aca="false">TEXT(A29,"yyyy-mm")</f>
         <v>2026-01</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="21" t="s">
+      <c r="D29" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="16" t="s">
         <v>228</v>
       </c>
-      <c r="F29" s="21" t="s">
+      <c r="F29" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="G29" s="21" t="s">
+      <c r="G29" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="H29" s="22" t="n">
+      <c r="H29" s="20" t="n">
         <f aca="false">IF(J29&gt;0,J29,0)</f>
         <v>200</v>
       </c>
-      <c r="I29" s="22" t="n">
+      <c r="I29" s="20" t="n">
         <f aca="false">IF(J29&lt;0,-J29,0)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="23" t="n">
+      <c r="J29" s="21" t="n">
         <v>200</v>
       </c>
-      <c r="K29" s="22" t="n">
+      <c r="K29" s="20" t="n">
         <f aca="false">K28+J29</f>
         <v>3430.77</v>
       </c>
-      <c r="L29" s="23" t="n">
+      <c r="L29" s="21" t="n">
         <v>3430.77</v>
       </c>
-      <c r="M29" s="22" t="n">
+      <c r="M29" s="20" t="n">
         <f aca="false">ROUND(K29-L29,2)</f>
         <v>0</v>
       </c>
-      <c r="N29" s="21" t="s">
+      <c r="N29" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15" t="n">
         <v>46040</v>
       </c>
-      <c r="B30" s="21" t="str">
+      <c r="B30" s="16" t="str">
         <f aca="false">TEXT(A30,"yyyy-mm")</f>
         <v>2026-01</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F30" s="21" t="s">
+      <c r="F30" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G30" s="21" t="s">
+      <c r="G30" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="H30" s="22" t="n">
+      <c r="H30" s="20" t="n">
         <f aca="false">IF(J30&gt;0,J30,0)</f>
         <v>300</v>
       </c>
-      <c r="I30" s="22" t="n">
+      <c r="I30" s="20" t="n">
         <f aca="false">IF(J30&lt;0,-J30,0)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="23" t="n">
+      <c r="J30" s="21" t="n">
         <v>300</v>
       </c>
-      <c r="K30" s="22" t="n">
+      <c r="K30" s="20" t="n">
         <f aca="false">K29+J30</f>
         <v>3730.77</v>
       </c>
-      <c r="L30" s="23" t="n">
+      <c r="L30" s="21" t="n">
         <v>3730.77</v>
       </c>
-      <c r="M30" s="22" t="n">
+      <c r="M30" s="20" t="n">
         <f aca="false">ROUND(K30-L30,2)</f>
         <v>0</v>
       </c>
-      <c r="N30" s="21" t="s">
+      <c r="N30" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15" t="n">
         <v>46041</v>
       </c>
-      <c r="B31" s="21" t="str">
+      <c r="B31" s="16" t="str">
         <f aca="false">TEXT(A31,"yyyy-mm")</f>
         <v>2026-01</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E31" s="21" t="s">
+      <c r="E31" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="F31" s="21" t="s">
+      <c r="F31" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G31" s="21" t="s">
+      <c r="G31" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="H31" s="22" t="n">
+      <c r="H31" s="20" t="n">
         <f aca="false">IF(J31&gt;0,J31,0)</f>
         <v>0</v>
       </c>
-      <c r="I31" s="22" t="n">
+      <c r="I31" s="20" t="n">
         <f aca="false">IF(J31&lt;0,-J31,0)</f>
         <v>1160.58</v>
       </c>
-      <c r="J31" s="23" t="n">
+      <c r="J31" s="21" t="n">
         <v>-1160.58</v>
       </c>
-      <c r="K31" s="22" t="n">
+      <c r="K31" s="20" t="n">
         <f aca="false">K30+J31</f>
         <v>2570.19</v>
       </c>
-      <c r="L31" s="23" t="n">
+      <c r="L31" s="21" t="n">
         <v>2570.19</v>
       </c>
-      <c r="M31" s="22" t="n">
+      <c r="M31" s="20" t="n">
         <f aca="false">ROUND(K31-L31,2)</f>
         <v>0</v>
       </c>
-      <c r="N31" s="21" t="s">
+      <c r="N31" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15" t="n">
         <v>46041</v>
       </c>
-      <c r="B32" s="21" t="str">
+      <c r="B32" s="16" t="str">
         <f aca="false">TEXT(A32,"yyyy-mm")</f>
         <v>2026-01</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="F32" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G32" s="21" t="s">
+      <c r="G32" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="H32" s="22" t="n">
+      <c r="H32" s="20" t="n">
         <f aca="false">IF(J32&gt;0,J32,0)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="22" t="n">
+      <c r="I32" s="20" t="n">
         <f aca="false">IF(J32&lt;0,-J32,0)</f>
         <v>2139.83</v>
       </c>
-      <c r="J32" s="23" t="n">
+      <c r="J32" s="21" t="n">
         <v>-2139.83</v>
       </c>
-      <c r="K32" s="22" t="n">
+      <c r="K32" s="20" t="n">
         <f aca="false">K31+J32</f>
         <v>430.360000000001</v>
       </c>
-      <c r="L32" s="23" t="n">
+      <c r="L32" s="21" t="n">
         <v>430.36</v>
       </c>
-      <c r="M32" s="22" t="n">
+      <c r="M32" s="20" t="n">
         <f aca="false">ROUND(K32-L32,2)</f>
         <v>0</v>
       </c>
-      <c r="N32" s="21" t="s">
+      <c r="N32" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="n">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15" t="n">
         <v>46043</v>
       </c>
-      <c r="B33" s="21" t="str">
+      <c r="B33" s="16" t="str">
         <f aca="false">TEXT(A33,"yyyy-mm")</f>
         <v>2026-01</v>
       </c>
-      <c r="C33" s="21" t="s">
+      <c r="C33" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="F33" s="21" t="s">
+      <c r="F33" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G33" s="21" t="s">
+      <c r="G33" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="H33" s="22" t="n">
+      <c r="H33" s="20" t="n">
         <f aca="false">IF(J33&gt;0,J33,0)</f>
         <v>600</v>
       </c>
-      <c r="I33" s="22" t="n">
+      <c r="I33" s="20" t="n">
         <f aca="false">IF(J33&lt;0,-J33,0)</f>
         <v>0</v>
       </c>
-      <c r="J33" s="23" t="n">
+      <c r="J33" s="21" t="n">
         <v>600</v>
       </c>
-      <c r="K33" s="22" t="n">
+      <c r="K33" s="20" t="n">
         <f aca="false">K32+J33</f>
         <v>1030.36</v>
       </c>
-      <c r="L33" s="23" t="n">
+      <c r="L33" s="21" t="n">
         <v>1030.36</v>
       </c>
-      <c r="M33" s="22" t="n">
+      <c r="M33" s="20" t="n">
         <f aca="false">ROUND(K33-L33,2)</f>
         <v>0</v>
       </c>
-      <c r="N33" s="21" t="s">
+      <c r="N33" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="20" t="n">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15" t="n">
         <v>46065</v>
       </c>
-      <c r="B34" s="21" t="str">
+      <c r="B34" s="16" t="str">
         <f aca="false">TEXT(A34,"yyyy-mm")</f>
         <v>2026-02</v>
       </c>
-      <c r="C34" s="21" t="s">
+      <c r="C34" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="D34" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="E34" s="21" t="s">
+      <c r="E34" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="F34" s="21" t="s">
+      <c r="F34" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="G34" s="21" t="s">
+      <c r="G34" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="H34" s="22" t="n">
+      <c r="H34" s="20" t="n">
         <f aca="false">IF(J34&gt;0,J34,0)</f>
         <v>1000</v>
       </c>
-      <c r="I34" s="22" t="n">
+      <c r="I34" s="20" t="n">
         <f aca="false">IF(J34&lt;0,-J34,0)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="23" t="n">
+      <c r="J34" s="21" t="n">
         <v>1000</v>
       </c>
-      <c r="K34" s="22" t="n">
+      <c r="K34" s="20" t="n">
         <f aca="false">K33+J34</f>
         <v>2030.36</v>
       </c>
-      <c r="L34" s="23" t="n">
+      <c r="L34" s="21" t="n">
         <v>2030.36</v>
       </c>
-      <c r="M34" s="22" t="n">
+      <c r="M34" s="20" t="n">
         <f aca="false">ROUND(K34-L34,2)</f>
         <v>0</v>
       </c>
-      <c r="N34" s="21" t="s">
+      <c r="N34" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="20" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15" t="n">
         <v>46069</v>
       </c>
-      <c r="B35" s="21" t="str">
+      <c r="B35" s="16" t="str">
         <f aca="false">TEXT(A35,"yyyy-mm")</f>
         <v>2026-02</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C35" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="E35" s="21" t="s">
+      <c r="E35" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="F35" s="21" t="s">
+      <c r="F35" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="G35" s="21" t="s">
+      <c r="G35" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="H35" s="22" t="n">
+      <c r="H35" s="20" t="n">
         <f aca="false">IF(J35&gt;0,J35,0)</f>
         <v>1400</v>
       </c>
-      <c r="I35" s="22" t="n">
+      <c r="I35" s="20" t="n">
         <f aca="false">IF(J35&lt;0,-J35,0)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="23" t="n">
+      <c r="J35" s="21" t="n">
         <v>1400</v>
       </c>
-      <c r="K35" s="22" t="n">
+      <c r="K35" s="20" t="n">
         <f aca="false">K34+J35</f>
         <v>3430.36</v>
       </c>
-      <c r="L35" s="23" t="n">
+      <c r="L35" s="21" t="n">
         <v>3430.36</v>
       </c>
-      <c r="M35" s="22" t="n">
+      <c r="M35" s="20" t="n">
         <f aca="false">ROUND(K35-L35,2)</f>
         <v>0</v>
       </c>
-      <c r="N35" s="21" t="s">
+      <c r="N35" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="20" t="n">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="15" t="n">
         <v>46070</v>
       </c>
-      <c r="B36" s="21" t="str">
+      <c r="B36" s="16" t="str">
         <f aca="false">TEXT(A36,"yyyy-mm")</f>
         <v>2026-02</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E36" s="21" t="s">
+      <c r="E36" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="F36" s="21" t="s">
+      <c r="F36" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G36" s="21" t="s">
+      <c r="G36" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="H36" s="22" t="n">
+      <c r="H36" s="20" t="n">
         <f aca="false">IF(J36&gt;0,J36,0)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="22" t="n">
+      <c r="I36" s="20" t="n">
         <f aca="false">IF(J36&lt;0,-J36,0)</f>
         <v>1160.58</v>
       </c>
-      <c r="J36" s="23" t="n">
+      <c r="J36" s="21" t="n">
         <v>-1160.58</v>
       </c>
-      <c r="K36" s="22" t="n">
+      <c r="K36" s="20" t="n">
         <f aca="false">K35+J36</f>
         <v>2269.78</v>
       </c>
-      <c r="L36" s="23" t="n">
+      <c r="L36" s="21" t="n">
         <v>2269.78</v>
       </c>
-      <c r="M36" s="22" t="n">
+      <c r="M36" s="20" t="n">
         <f aca="false">ROUND(K36-L36,2)</f>
         <v>0</v>
       </c>
-      <c r="N36" s="21" t="s">
+      <c r="N36" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="n">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="15" t="n">
         <v>46070</v>
       </c>
-      <c r="B37" s="21" t="str">
+      <c r="B37" s="16" t="str">
         <f aca="false">TEXT(A37,"yyyy-mm")</f>
         <v>2026-02</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="F37" s="21" t="s">
+      <c r="F37" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="G37" s="21" t="s">
+      <c r="G37" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="H37" s="22" t="n">
+      <c r="H37" s="20" t="n">
         <f aca="false">IF(J37&gt;0,J37,0)</f>
         <v>0</v>
       </c>
-      <c r="I37" s="22" t="n">
+      <c r="I37" s="20" t="n">
         <f aca="false">IF(J37&lt;0,-J37,0)</f>
         <v>2139.83</v>
       </c>
-      <c r="J37" s="23" t="n">
+      <c r="J37" s="21" t="n">
         <v>-2139.83</v>
       </c>
-      <c r="K37" s="22" t="n">
+      <c r="K37" s="20" t="n">
         <f aca="false">K36+J37</f>
         <v>129.950000000001</v>
       </c>
-      <c r="L37" s="23" t="n">
+      <c r="L37" s="21" t="n">
         <v>129.95</v>
       </c>
-      <c r="M37" s="22" t="n">
+      <c r="M37" s="20" t="n">
         <f aca="false">ROUND(K37-L37,2)</f>
         <v>0</v>
       </c>
-      <c r="N37" s="21" t="s">
+      <c r="N37" s="16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G38" s="24" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G38" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="H38" s="25" t="n">
+      <c r="H38" s="22" t="n">
         <f aca="false">SUM(H2:H37)</f>
         <v>24332</v>
       </c>
-      <c r="I38" s="25" t="n">
+      <c r="I38" s="22" t="n">
         <f aca="false">SUM(I2:I37)</f>
         <v>24202.05</v>
       </c>
-      <c r="J38" s="25" t="n">
+      <c r="J38" s="22" t="n">
         <f aca="false">SUM(J2:J37)</f>
         <v>129.950000000001</v>
       </c>
@@ -5884,23 +6239,23 @@
   <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="44"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="26" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="27" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>237</v>
       </c>
     </row>
@@ -5942,296 +6297,296 @@
         <v>245</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B5" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="30" t="n">
+      <c r="B5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="24" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$H:$H,'Monzo Transactions'!$B:$B,$A5)</f>
         <v>7682</v>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="24" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$I:$I,'Monzo Transactions'!$B:$B,$A5)</f>
         <v>3000</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="24" t="n">
         <f aca="false">B5+C5-D5</f>
         <v>4682</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="23" t="n">
         <v>4682</v>
       </c>
-      <c r="G5" s="30" t="n">
+      <c r="G5" s="24" t="n">
         <f aca="false">ROUND(E5-F5,2)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="29" t="n">
+      <c r="H5" s="23" t="n">
         <v>7682</v>
       </c>
-      <c r="I5" s="29" t="n">
+      <c r="I5" s="23" t="n">
         <v>3000</v>
       </c>
-      <c r="J5" s="30" t="n">
+      <c r="J5" s="24" t="n">
         <f aca="false">ROUND((C5-H5)+(D5-I5),2)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="28" t="str">
+      <c r="K5" s="5" t="str">
         <f aca="false">IF(AND(G5=0,OR(J5=0,J5="n/a")),"Reconciled","CHECK")</f>
         <v>Reconciled</v>
       </c>
-      <c r="L5" s="28" t="s">
+      <c r="L5" s="5" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B6" s="30" t="n">
+      <c r="B6" s="24" t="n">
         <f aca="false">F5</f>
         <v>4682</v>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="24" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$H:$H,'Monzo Transactions'!$B:$B,$A6)</f>
         <v>5550</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="24" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$I:$I,'Monzo Transactions'!$B:$B,$A6)</f>
         <v>7800.41</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="24" t="n">
         <f aca="false">B6+C6-D6</f>
         <v>2431.59</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="23" t="n">
         <v>2431.59</v>
       </c>
-      <c r="G6" s="30" t="n">
+      <c r="G6" s="24" t="n">
         <f aca="false">ROUND(E6-F6,2)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="29" t="n">
+      <c r="H6" s="23" t="n">
         <v>5550</v>
       </c>
-      <c r="I6" s="29" t="n">
+      <c r="I6" s="23" t="n">
         <v>7800.41</v>
       </c>
-      <c r="J6" s="30" t="n">
+      <c r="J6" s="24" t="n">
         <f aca="false">ROUND((C6-H6)+(D6-I6),2)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="28" t="str">
+      <c r="K6" s="5" t="str">
         <f aca="false">IF(AND(G6=0,OR(J6=0,J6="n/a")),"Reconciled","CHECK")</f>
         <v>Reconciled</v>
       </c>
-      <c r="L6" s="28" t="s">
+      <c r="L6" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="24" t="n">
         <f aca="false">F6</f>
         <v>2431.59</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="24" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$H:$H,'Monzo Transactions'!$B:$B,$A7)</f>
         <v>1000</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="24" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$I:$I,'Monzo Transactions'!$B:$B,$A7)</f>
         <v>3300.41</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="24" t="n">
         <f aca="false">B7+C7-D7</f>
         <v>131.18</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="23" t="n">
         <v>131.18</v>
       </c>
-      <c r="G7" s="30" t="n">
+      <c r="G7" s="24" t="n">
         <f aca="false">ROUND(E7-F7,2)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="29" t="n">
+      <c r="H7" s="23" t="n">
         <v>1000</v>
       </c>
-      <c r="I7" s="29" t="n">
+      <c r="I7" s="23" t="n">
         <v>3300.41</v>
       </c>
-      <c r="J7" s="30" t="n">
+      <c r="J7" s="24" t="n">
         <f aca="false">ROUND((C7-H7)+(D7-I7),2)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="28" t="str">
+      <c r="K7" s="5" t="str">
         <f aca="false">IF(AND(G7=0,OR(J7=0,J7="n/a")),"Reconciled","CHECK")</f>
         <v>Reconciled</v>
       </c>
-      <c r="L7" s="28" t="s">
+      <c r="L7" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="24" t="n">
         <f aca="false">F7</f>
         <v>131.18</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="24" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$H:$H,'Monzo Transactions'!$B:$B,$A8)</f>
         <v>5300</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="24" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$I:$I,'Monzo Transactions'!$B:$B,$A8)</f>
         <v>3500.41</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="24" t="n">
         <f aca="false">B8+C8-D8</f>
         <v>1930.77</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="23" t="n">
         <v>1930.77</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="24" t="n">
         <f aca="false">ROUND(E8-F8,2)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="30" t="s">
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="K8" s="28" t="str">
+      <c r="K8" s="5" t="str">
         <f aca="false">IF(AND(G8=0,OR(J8=0,J8="n/a")),"Reconciled","CHECK")</f>
         <v>Reconciled</v>
       </c>
-      <c r="L8" s="28" t="s">
+      <c r="L8" s="5" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B9" s="30" t="n">
+      <c r="B9" s="24" t="n">
         <f aca="false">F8</f>
         <v>1930.77</v>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="24" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$H:$H,'Monzo Transactions'!$B:$B,$A9)</f>
         <v>2400</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="24" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$I:$I,'Monzo Transactions'!$B:$B,$A9)</f>
         <v>3300.41</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="24" t="n">
         <f aca="false">B9+C9-D9</f>
         <v>1030.36</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="23" t="n">
         <v>1030.36</v>
       </c>
-      <c r="G9" s="30" t="n">
+      <c r="G9" s="24" t="n">
         <f aca="false">ROUND(E9-F9,2)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="30" t="s">
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="K9" s="28" t="str">
+      <c r="K9" s="5" t="str">
         <f aca="false">IF(AND(G9=0,OR(J9=0,J9="n/a")),"Reconciled","CHECK")</f>
         <v>Reconciled</v>
       </c>
-      <c r="L9" s="28" t="s">
+      <c r="L9" s="5" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="24" t="n">
         <f aca="false">F9</f>
         <v>1030.36</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="24" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$H:$H,'Monzo Transactions'!$B:$B,$A10)</f>
         <v>2400</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="24" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$I:$I,'Monzo Transactions'!$B:$B,$A10)</f>
         <v>3300.41</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="24" t="n">
         <f aca="false">B10+C10-D10</f>
         <v>129.95</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="23" t="n">
         <v>129.95</v>
       </c>
-      <c r="G10" s="30" t="n">
+      <c r="G10" s="24" t="n">
         <f aca="false">ROUND(E10-F10,2)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="30" t="s">
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="K10" s="28" t="str">
+      <c r="K10" s="5" t="str">
         <f aca="false">IF(AND(G10=0,OR(J10=0,J10="n/a")),"Reconciled","CHECK")</f>
         <v>Reconciled</v>
       </c>
-      <c r="L10" s="28" t="s">
+      <c r="L10" s="5" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="31" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32" t="n">
+      <c r="B11" s="26"/>
+      <c r="C11" s="26" t="n">
         <f aca="false">SUM(C5:C10)</f>
         <v>24332</v>
       </c>
-      <c r="D11" s="32" t="n">
+      <c r="D11" s="26" t="n">
         <f aca="false">SUM(D5:D10)</f>
         <v>24202.05</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="26" t="n">
         <f aca="false">B5+C11-D11</f>
         <v>129.950000000001</v>
       </c>
-      <c r="F11" s="32" t="n">
+      <c r="F11" s="26" t="n">
         <f aca="false">F10</f>
         <v>129.95</v>
       </c>
-      <c r="G11" s="32" t="n">
+      <c r="G11" s="26" t="n">
         <f aca="false">ROUND(E11-F11,2)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="D13" s="24" t="n">
+      <c r="D13" s="18" t="n">
         <f aca="false">COUNTIF('Monzo Transactions'!M2:M37,"&lt;&gt;0")</f>
         <v>0</v>
       </c>
@@ -6256,471 +6611,1851 @@
   <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="70"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B5" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>2100</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>1900</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <f aca="false">SUM(B5:G5)</f>
+        <v>4000</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A5)</f>
+        <v>6</v>
+      </c>
+      <c r="J5" s="29"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>-1000</v>
+      </c>
+      <c r="D6" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>2000</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>200</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>1400</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <f aca="false">SUM(B6:G6)</f>
+        <v>2600</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A6)</f>
+        <v>4</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>6400</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>1000</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <f aca="false">SUM(B7:G7)</f>
+        <v>7400</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A7)</f>
+        <v>3</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>1282</v>
+      </c>
+      <c r="C8" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>5550</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>300</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <f aca="false">SUM(B8:G8)</f>
+        <v>7132</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A8)</f>
+        <v>6</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>1000</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>1200</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <f aca="false">SUM(B9:G9)</f>
+        <v>2200</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A9)</f>
+        <v>3</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>-3000</v>
+      </c>
+      <c r="C10" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>-1500</v>
+      </c>
+      <c r="D10" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="28" t="n">
+        <f aca="false">SUM(B10:G10)</f>
+        <v>-4500</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A10)</f>
+        <v>2</v>
+      </c>
+      <c r="J10" s="29"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>-1160.58</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>-1160.58</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>-1160.58</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>-1160.58</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>-1160.58</v>
+      </c>
+      <c r="H11" s="28" t="n">
+        <f aca="false">SUM(B11:G11)</f>
+        <v>-5802.9</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A11)</f>
+        <v>5</v>
+      </c>
+      <c r="J11" s="29"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B12" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>-2139.83</v>
+      </c>
+      <c r="D12" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>-2139.83</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>-2139.83</v>
+      </c>
+      <c r="F12" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>-2139.83</v>
+      </c>
+      <c r="G12" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>-2139.83</v>
+      </c>
+      <c r="H12" s="28" t="n">
+        <f aca="false">SUM(B12:G12)</f>
+        <v>-10699.15</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A12)</f>
+        <v>5</v>
+      </c>
+      <c r="J12" s="29"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,B$4)</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,C$4)</f>
+        <v>-2000</v>
+      </c>
+      <c r="D13" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,D$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,E$4)</f>
+        <v>-200</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,F$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,G$4)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="28" t="n">
+        <f aca="false">SUM(B13:G13)</f>
+        <v>-2200</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A13)</f>
+        <v>2</v>
+      </c>
+      <c r="J13" s="29" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="26" t="s">
+        <v>267</v>
+      </c>
+      <c r="B14" s="26" t="n">
+        <f aca="false">SUM(B5:B13)</f>
+        <v>4682</v>
+      </c>
+      <c r="C14" s="26" t="n">
+        <f aca="false">SUM(C5:C13)</f>
+        <v>-2250.41</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <f aca="false">SUM(D5:D13)</f>
+        <v>-2300.41</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <f aca="false">SUM(E5:E13)</f>
+        <v>1799.59</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <f aca="false">SUM(F5:F13)</f>
+        <v>-900.41</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <f aca="false">SUM(G5:G13)</f>
+        <v>-900.41</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <f aca="false">SUM(H5:H13)</f>
+        <v>129.950000000001</v>
+      </c>
+      <c r="I14" s="30" t="n">
+        <f aca="false">SUM(I5:I13)</f>
+        <v>36</v>
+      </c>
+      <c r="J14" s="26"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B15" s="31" t="n">
+        <f aca="false">ROUND(B14-('Monzo Reconciliation'!C5-'Monzo Reconciliation'!D5),2)</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <f aca="false">ROUND(C14-('Monzo Reconciliation'!C6-'Monzo Reconciliation'!D6),2)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="31" t="n">
+        <f aca="false">ROUND(D14-('Monzo Reconciliation'!C7-'Monzo Reconciliation'!D7),2)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="31" t="n">
+        <f aca="false">ROUND(E14-('Monzo Reconciliation'!C8-'Monzo Reconciliation'!D8),2)</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="31" t="n">
+        <f aca="false">ROUND(F14-('Monzo Reconciliation'!C9-'Monzo Reconciliation'!D9),2)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="31" t="n">
+        <f aca="false">ROUND(G14-('Monzo Reconciliation'!C10-'Monzo Reconciliation'!D10),2)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G46"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="33" t="n">
+        <v>133528</v>
+      </c>
+      <c r="D2" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="34" t="n">
+        <f aca="false">D2+E2</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="C3" s="33" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="34" t="n">
+        <f aca="false">D3+E3</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="33" t="n">
+        <v>650</v>
+      </c>
+      <c r="E4" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="F4" s="34" t="n">
+        <f aca="false">D4+E4</f>
+        <v>780</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="C5" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="34" t="n">
+        <f aca="false">D5+E5</f>
+        <v>42</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="33" t="n">
+        <v>200</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <f aca="false">D6+E6</f>
+        <v>240</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>285</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>300</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <f aca="false">D7+E7</f>
+        <v>360</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>29</v>
+      </c>
+      <c r="E8" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <f aca="false">D8+E8</f>
+        <v>29</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <f aca="false">D9+E9</f>
+        <v>18</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="C10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <f aca="false">D10+E10</f>
+        <v>45</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="C11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <f aca="false">D11+E11</f>
+        <v>14</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <f aca="false">D12+E12</f>
+        <v>7</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="C13" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <f aca="false">D13+E13</f>
+        <v>45</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="C14" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="34" t="n">
+        <f aca="false">D14+E14</f>
+        <v>15</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>293</v>
+      </c>
+      <c r="C15" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="34" t="n">
+        <f aca="false">D15+E15</f>
+        <v>15</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="33" t="n">
+        <v>60</v>
+      </c>
+      <c r="E16" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="34" t="n">
+        <f aca="false">D16+E16</f>
+        <v>60</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="C17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>131958</v>
+      </c>
+      <c r="E17" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="34" t="n">
+        <f aca="false">D17+E17</f>
+        <v>131958</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>298</v>
+      </c>
+      <c r="C18" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="33" t="n">
+        <v>462000</v>
+      </c>
+      <c r="E18" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="34" t="n">
+        <f aca="false">D18+E18</f>
+        <v>462000</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>300</v>
+      </c>
+      <c r="C19" s="33" t="n">
+        <v>400</v>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="34" t="n">
+        <f aca="false">D19+E19</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="32" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="C20" s="33" t="n">
+        <v>311938.6</v>
+      </c>
+      <c r="D20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="34" t="n">
+        <f aca="false">D20+E20</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>303</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>131958</v>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="34" t="n">
+        <f aca="false">D21+E21</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="32" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>304</v>
+      </c>
+      <c r="C22" s="33" t="n">
+        <v>18362.34</v>
+      </c>
+      <c r="D22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="34" t="n">
+        <f aca="false">D22+E22</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="C23" s="33" t="n">
+        <v>38000</v>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="34" t="n">
+        <f aca="false">D23+E23</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="C24" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>775</v>
+      </c>
+      <c r="E24" s="33" t="n">
+        <v>155</v>
+      </c>
+      <c r="F24" s="34" t="n">
+        <f aca="false">D24+E24</f>
+        <v>930</v>
+      </c>
+      <c r="G24" s="32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>309</v>
+      </c>
+      <c r="C25" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="33" t="n">
+        <v>100</v>
+      </c>
+      <c r="E25" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" s="34" t="n">
+        <f aca="false">D25+E25</f>
+        <v>120</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="C26" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="33" t="n">
+        <v>35</v>
+      </c>
+      <c r="E26" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F26" s="34" t="n">
+        <f aca="false">D26+E26</f>
+        <v>42</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="C27" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="33" t="n">
+        <v>75</v>
+      </c>
+      <c r="E27" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="F27" s="34" t="n">
+        <f aca="false">D27+E27</f>
+        <v>90</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>312</v>
+      </c>
+      <c r="C28" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="33" t="n">
+        <v>60</v>
+      </c>
+      <c r="E28" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" s="34" t="n">
+        <f aca="false">D28+E28</f>
+        <v>72</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>313</v>
+      </c>
+      <c r="C29" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="33" t="n">
+        <v>300</v>
+      </c>
+      <c r="E29" s="33" t="n">
+        <v>60</v>
+      </c>
+      <c r="F29" s="34" t="n">
+        <f aca="false">D29+E29</f>
+        <v>360</v>
+      </c>
+      <c r="G29" s="32" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="C30" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="33" t="n">
+        <v>50</v>
+      </c>
+      <c r="E30" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" s="34" t="n">
+        <f aca="false">D30+E30</f>
+        <v>60</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="C31" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="34" t="n">
+        <f aca="false">D31+E31</f>
+        <v>7</v>
+      </c>
+      <c r="G31" s="32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="C32" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="E32" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="34" t="n">
+        <f aca="false">D32+E32</f>
+        <v>18</v>
+      </c>
+      <c r="G32" s="32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="C33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="33" t="n">
+        <v>45</v>
+      </c>
+      <c r="E33" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="34" t="n">
+        <f aca="false">D33+E33</f>
+        <v>45</v>
+      </c>
+      <c r="G33" s="32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="C34" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="33" t="n">
+        <v>109.66</v>
+      </c>
+      <c r="E34" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="34" t="n">
+        <f aca="false">D34+E34</f>
+        <v>109.66</v>
+      </c>
+      <c r="G34" s="32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="C35" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="E35" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="34" t="n">
+        <f aca="false">D35+E35</f>
+        <v>150</v>
+      </c>
+      <c r="G35" s="32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>318</v>
+      </c>
+      <c r="C36" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="33" t="n">
+        <v>36200</v>
+      </c>
+      <c r="E36" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="34" t="n">
+        <f aca="false">D36+E36</f>
+        <v>36200</v>
+      </c>
+      <c r="G36" s="32" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="C37" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="33" t="n">
+        <v>200.28</v>
+      </c>
+      <c r="E37" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="34" t="n">
+        <f aca="false">D37+E37</f>
+        <v>200.28</v>
+      </c>
+      <c r="G37" s="32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>321</v>
+      </c>
+      <c r="C38" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="33" t="n">
+        <v>60</v>
+      </c>
+      <c r="E38" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="34" t="n">
+        <f aca="false">D38+E38</f>
+        <v>60</v>
+      </c>
+      <c r="G38" s="32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="C39" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="34" t="n">
+        <f aca="false">D39+E39</f>
+        <v>15</v>
+      </c>
+      <c r="G39" s="32" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B40" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="C40" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="E40" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="34" t="n">
+        <f aca="false">D40+E40</f>
+        <v>20</v>
+      </c>
+      <c r="G40" s="32" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="C41" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="33" t="n">
+        <v>160</v>
+      </c>
+      <c r="E41" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="34" t="n">
+        <f aca="false">D41+E41</f>
+        <v>160</v>
+      </c>
+      <c r="G41" s="32" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="35" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="36" t="s">
+        <v>269</v>
+      </c>
+      <c r="B44" s="37"/>
+      <c r="C44" s="36" t="s">
+        <v>326</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="E44" s="36" t="s">
+        <v>328</v>
+      </c>
+      <c r="F44" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="G44" s="36" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="B45" s="38" t="s">
+        <v>330</v>
+      </c>
+      <c r="C45" s="34" t="n">
+        <f aca="false">SUMIFS($C$2:$C$41,$A$2:$A$41,$A45)</f>
+        <v>133628</v>
+      </c>
+      <c r="D45" s="33" t="n">
+        <v>133628</v>
+      </c>
+      <c r="E45" s="34" t="n">
+        <f aca="false">SUMIFS($F$2:$F$41,$A$2:$A$41,$A45)</f>
+        <v>133628</v>
+      </c>
+      <c r="F45" s="33" t="n">
+        <v>133628</v>
+      </c>
+      <c r="G45" s="35" t="str">
+        <f aca="false">IF(AND(ROUND(C45-D45,2)=0,ROUND(E45-F45,2)=0,ROUND(C45-E45,2)=0),"Agrees – balances to £0","CHECK")</f>
+        <v>Agrees – balances to £0</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="32" t="s">
+        <v>297</v>
+      </c>
+      <c r="B46" s="38" t="s">
+        <v>331</v>
+      </c>
+      <c r="C46" s="34" t="n">
+        <f aca="false">SUMIFS($C$2:$C$41,$A$2:$A$41,$A46)</f>
+        <v>500658.94</v>
+      </c>
+      <c r="D46" s="33" t="n">
+        <v>500658.94</v>
+      </c>
+      <c r="E46" s="34" t="n">
+        <f aca="false">SUMIFS($F$2:$F$41,$A$2:$A$41,$A46)</f>
+        <v>500658.94</v>
+      </c>
+      <c r="F46" s="33" t="n">
+        <v>500658.94</v>
+      </c>
+      <c r="G46" s="35" t="str">
+        <f aca="false">IF(AND(ROUND(C46-D46,2)=0,ROUND(E46-F46,2)=0,ROUND(C46-E46,2)=0),"Agrees – balances to £0","CHECK")</f>
+        <v>Agrees – balances to £0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G41"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="75"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="26" t="s">
-        <v>259</v>
+      <c r="A1" s="39" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="27" t="s">
-        <v>260</v>
+      <c r="A2" s="38" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>246</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>248</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>250</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>252</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>255</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="J4" s="33" t="s">
+      <c r="A4" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="C4" s="36" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="B5" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,B$4)</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,C$4)</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,D$4)</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,E$4)</f>
-        <v>2100</v>
-      </c>
-      <c r="F5" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,F$4)</f>
-        <v>1900</v>
-      </c>
-      <c r="G5" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,G$4)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="35" t="n">
-        <f aca="false">SUM(B5:G5)</f>
-        <v>4000</v>
-      </c>
-      <c r="I5" s="28" t="n">
-        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A5)</f>
-        <v>6</v>
-      </c>
-      <c r="J5" s="36"/>
+      <c r="A5" s="40" t="s">
+        <v>336</v>
+      </c>
+      <c r="B5" s="41" t="n">
+        <f aca="false">SUMIFS('Completion Lines'!$F$2:$F$41,'Completion Lines'!$G$2:$G$41,"Property cost – purchase price")</f>
+        <v>462000</v>
+      </c>
+      <c r="C5" s="42"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="B6" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,B$4)</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,C$4)</f>
-        <v>-1000</v>
-      </c>
-      <c r="D6" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,D$4)</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,E$4)</f>
-        <v>2000</v>
-      </c>
-      <c r="F6" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,F$4)</f>
-        <v>200</v>
-      </c>
-      <c r="G6" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,G$4)</f>
-        <v>1400</v>
-      </c>
-      <c r="H6" s="35" t="n">
-        <f aca="false">SUM(B6:G6)</f>
-        <v>2600</v>
-      </c>
-      <c r="I6" s="28" t="n">
-        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A6)</f>
-        <v>4</v>
-      </c>
-      <c r="J6" s="36" t="s">
-        <v>262</v>
+      <c r="A6" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="B6" s="41" t="n">
+        <f aca="false">SUMIFS('Completion Lines'!$F$2:$F$41,'Completion Lines'!$G$2:$G$41,"Property cost – Stamp Duty (SDLT)")</f>
+        <v>36200</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="B7" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,B$4)</f>
-        <v>6400</v>
-      </c>
-      <c r="C7" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,C$4)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,D$4)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,E$4)</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,F$4)</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,G$4)</f>
-        <v>1000</v>
-      </c>
-      <c r="H7" s="35" t="n">
-        <f aca="false">SUM(B7:G7)</f>
-        <v>7400</v>
-      </c>
-      <c r="I7" s="28" t="n">
-        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A7)</f>
-        <v>3</v>
-      </c>
-      <c r="J7" s="36" t="s">
-        <v>263</v>
+      <c r="A7" s="40" t="s">
+        <v>339</v>
+      </c>
+      <c r="B7" s="41" t="n">
+        <f aca="false">SUMIFS('Completion Lines'!$F$2:$F$41,'Completion Lines'!$G$2:$G$41,"Property cost – legal &amp; acquisition fees")</f>
+        <v>1743.94</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="28" t="s">
-        <v>193</v>
-      </c>
-      <c r="B8" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,B$4)</f>
-        <v>1282</v>
-      </c>
-      <c r="C8" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,C$4)</f>
-        <v>5550</v>
-      </c>
-      <c r="D8" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,D$4)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,E$4)</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,F$4)</f>
-        <v>300</v>
-      </c>
-      <c r="G8" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,G$4)</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="35" t="n">
-        <f aca="false">SUM(B8:G8)</f>
-        <v>7132</v>
-      </c>
-      <c r="I8" s="28" t="n">
-        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A8)</f>
-        <v>6</v>
-      </c>
-      <c r="J8" s="36" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="B9" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,B$4)</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,C$4)</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,D$4)</f>
-        <v>1000</v>
-      </c>
-      <c r="E9" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,E$4)</f>
-        <v>1200</v>
-      </c>
-      <c r="F9" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,F$4)</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,G$4)</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="35" t="n">
-        <f aca="false">SUM(B9:G9)</f>
-        <v>2200</v>
-      </c>
-      <c r="I9" s="28" t="n">
-        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A9)</f>
-        <v>3</v>
-      </c>
-      <c r="J9" s="36" t="s">
-        <v>265</v>
-      </c>
+      <c r="A8" s="43" t="s">
+        <v>341</v>
+      </c>
+      <c r="B8" s="44" t="n">
+        <f aca="false">SUM(B5:B7)</f>
+        <v>499943.94</v>
+      </c>
+      <c r="C8" s="43"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="B10" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,B$4)</f>
-        <v>-3000</v>
-      </c>
-      <c r="C10" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,C$4)</f>
-        <v>-1500</v>
-      </c>
-      <c r="D10" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,D$4)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,E$4)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,F$4)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,G$4)</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="35" t="n">
-        <f aca="false">SUM(B10:G10)</f>
-        <v>-4500</v>
-      </c>
-      <c r="I10" s="28" t="n">
-        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A10)</f>
-        <v>2</v>
-      </c>
-      <c r="J10" s="36"/>
+      <c r="A10" s="36" t="s">
+        <v>342</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="B11" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,B$4)</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,C$4)</f>
-        <v>-1160.58</v>
-      </c>
-      <c r="D11" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,D$4)</f>
-        <v>-1160.58</v>
-      </c>
-      <c r="E11" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,E$4)</f>
-        <v>-1160.58</v>
-      </c>
-      <c r="F11" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,F$4)</f>
-        <v>-1160.58</v>
-      </c>
-      <c r="G11" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,G$4)</f>
-        <v>-1160.58</v>
-      </c>
-      <c r="H11" s="35" t="n">
-        <f aca="false">SUM(B11:G11)</f>
-        <v>-5802.9</v>
-      </c>
-      <c r="I11" s="28" t="n">
-        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A11)</f>
-        <v>5</v>
-      </c>
-      <c r="J11" s="36"/>
+      <c r="A11" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="B11" s="41" t="n">
+        <f aca="false">SUMIFS('Completion Lines'!$F$2:$F$41,'Completion Lines'!$G$2:$G$41,"Finance cost – Cairnsford mortgage")</f>
+        <v>715</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="B12" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,B$4)</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,C$4)</f>
-        <v>-2139.83</v>
-      </c>
-      <c r="D12" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,D$4)</f>
-        <v>-2139.83</v>
-      </c>
-      <c r="E12" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,E$4)</f>
-        <v>-2139.83</v>
-      </c>
-      <c r="F12" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,F$4)</f>
-        <v>-2139.83</v>
-      </c>
-      <c r="G12" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,G$4)</f>
-        <v>-2139.83</v>
-      </c>
-      <c r="H12" s="35" t="n">
-        <f aca="false">SUM(B12:G12)</f>
-        <v>-10699.15</v>
-      </c>
-      <c r="I12" s="28" t="n">
-        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A12)</f>
-        <v>5</v>
-      </c>
-      <c r="J12" s="36"/>
+      <c r="A12" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="B12" s="41" t="n">
+        <f aca="false">SUMIFS('Completion Lines'!$F$2:$F$41,'Completion Lines'!$G$2:$G$41,"Finance cost – Strensall remortgage")</f>
+        <v>1670</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="B13" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,B$4)</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,C$4)</f>
-        <v>-2000</v>
-      </c>
-      <c r="D13" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,D$4)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,E$4)</f>
-        <v>-200</v>
-      </c>
-      <c r="F13" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,F$4)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="34" t="n">
-        <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,G$4)</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="35" t="n">
-        <f aca="false">SUM(B13:G13)</f>
-        <v>-2200</v>
-      </c>
-      <c r="I13" s="28" t="n">
-        <f aca="false">COUNTIFS('Monzo Transactions'!$G:$G,$A13)</f>
-        <v>2</v>
-      </c>
-      <c r="J13" s="36" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="B14" s="32" t="n">
-        <f aca="false">SUM(B5:B13)</f>
-        <v>4682</v>
-      </c>
-      <c r="C14" s="32" t="n">
-        <f aca="false">SUM(C5:C13)</f>
-        <v>-2250.41</v>
-      </c>
-      <c r="D14" s="32" t="n">
-        <f aca="false">SUM(D5:D13)</f>
-        <v>-2300.41</v>
-      </c>
-      <c r="E14" s="32" t="n">
-        <f aca="false">SUM(E5:E13)</f>
-        <v>1799.59</v>
-      </c>
-      <c r="F14" s="32" t="n">
-        <f aca="false">SUM(F5:F13)</f>
-        <v>-900.41</v>
-      </c>
-      <c r="G14" s="32" t="n">
-        <f aca="false">SUM(G5:G13)</f>
-        <v>-900.41</v>
-      </c>
-      <c r="H14" s="32" t="n">
-        <f aca="false">SUM(H5:H13)</f>
-        <v>129.950000000001</v>
-      </c>
-      <c r="I14" s="37" t="n">
-        <f aca="false">SUM(I5:I13)</f>
-        <v>36</v>
-      </c>
-      <c r="J14" s="32"/>
+      <c r="A13" s="43" t="s">
+        <v>347</v>
+      </c>
+      <c r="B13" s="44" t="n">
+        <f aca="false">SUM(B11:B12)</f>
+        <v>2385</v>
+      </c>
+      <c r="C13" s="43"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="B15" s="38" t="n">
-        <f aca="false">ROUND(B14-('Monzo Reconciliation'!C5-'Monzo Reconciliation'!D5),2)</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="38" t="n">
-        <f aca="false">ROUND(C14-('Monzo Reconciliation'!C6-'Monzo Reconciliation'!D6),2)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="38" t="n">
-        <f aca="false">ROUND(D14-('Monzo Reconciliation'!C7-'Monzo Reconciliation'!D7),2)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="38" t="n">
-        <f aca="false">ROUND(E14-('Monzo Reconciliation'!C8-'Monzo Reconciliation'!D8),2)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="38" t="n">
-        <f aca="false">ROUND(F14-('Monzo Reconciliation'!C9-'Monzo Reconciliation'!D9),2)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="38" t="n">
-        <f aca="false">ROUND(G14-('Monzo Reconciliation'!C10-'Monzo Reconciliation'!D10),2)</f>
-        <v>0</v>
+      <c r="A15" s="36" t="s">
+        <v>348</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="40" t="s">
+        <v>349</v>
+      </c>
+      <c r="B16" s="41" t="n">
+        <f aca="false">SUMIFS('Completion Lines'!$C$2:$C$41,'Completion Lines'!$G$2:$G$41,"Funding – Together Commercial mortgage (net)")</f>
+        <v>311938.6</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="40" t="s">
+        <v>351</v>
+      </c>
+      <c r="B17" s="41" t="n">
+        <f aca="false">SUMIFS('Completion Lines'!$C$2:$C$41,'Completion Lines'!$G$2:$G$41,"Transfer – Strensall proceeds to Cairnsford",'Completion Lines'!$A$2:$A$41,"36 Cairnsford Rd – Purchase (17/07/2025)")</f>
+        <v>131958</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="40" t="s">
+        <v>353</v>
+      </c>
+      <c r="B18" s="41" t="n">
+        <f aca="false">SUMIFS('Completion Lines'!$C$2:$C$41,'Completion Lines'!$G$2:$G$41,"Funding – Alvine Tchega")</f>
+        <v>18362.34</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="40" t="s">
+        <v>355</v>
+      </c>
+      <c r="B19" s="41" t="n">
+        <f aca="false">SUMIFS('Completion Lines'!$C$2:$C$41,'Completion Lines'!$G$2:$G$41,"Funding – Kakmeni")</f>
+        <v>38000</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="40" t="s">
+        <v>357</v>
+      </c>
+      <c r="B20" s="41" t="n">
+        <f aca="false">SUMIFS('Completion Lines'!$C$2:$C$41,'Completion Lines'!$G$2:$G$41,"Funding – money on account",'Completion Lines'!$A$2:$A$41,"36 Cairnsford Rd – Purchase (17/07/2025)")</f>
+        <v>400</v>
+      </c>
+      <c r="C20" s="42"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="43" t="s">
+        <v>358</v>
+      </c>
+      <c r="B21" s="44" t="n">
+        <f aca="false">SUM(B16:B20)</f>
+        <v>500658.94</v>
+      </c>
+      <c r="C21" s="43"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="36" t="s">
+        <v>359</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="40" t="s">
+        <v>360</v>
+      </c>
+      <c r="B24" s="41" t="n">
+        <f aca="false">B8+B11</f>
+        <v>500658.94</v>
+      </c>
+      <c r="C24" s="42"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="40" t="s">
+        <v>361</v>
+      </c>
+      <c r="B25" s="41" t="n">
+        <f aca="false">B21</f>
+        <v>500658.94</v>
+      </c>
+      <c r="C25" s="42"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="35" t="s">
+        <v>362</v>
+      </c>
+      <c r="B26" s="45" t="n">
+        <f aca="false">ROUND(B24-B25,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="36" t="s">
+        <v>363</v>
+      </c>
+      <c r="B28" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="40" t="s">
+        <v>364</v>
+      </c>
+      <c r="B29" s="41" t="n">
+        <f aca="false">-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$E:$E,"10395974-002")</f>
+        <v>10699.15</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="40" t="s">
+        <v>366</v>
+      </c>
+      <c r="B30" s="41" t="n">
+        <f aca="false">-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$E:$E,"10395973-002")</f>
+        <v>5802.9</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
